--- a/research/traditional_assets/database/data/kuwait/kuwait_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_retail_automotive.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="kwse_alg" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04945</v>
+        <v>0.0001649999999999998</v>
       </c>
       <c r="E2">
-        <v>0.02023</v>
+        <v>-0.005899999999999999</v>
       </c>
       <c r="G2">
-        <v>-0.002173622704507512</v>
+        <v>0.04630456121981546</v>
       </c>
       <c r="H2">
-        <v>-0.002173622704507512</v>
+        <v>0.04630456121981546</v>
       </c>
       <c r="I2">
-        <v>-0.0147245409015025</v>
+        <v>0.03196976777760588</v>
       </c>
       <c r="J2">
-        <v>-0.01450557293970013</v>
+        <v>0.0316699137486849</v>
       </c>
       <c r="K2">
-        <v>28.1</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="L2">
-        <v>0.03127434613244296</v>
+        <v>0.04914599829854067</v>
       </c>
       <c r="M2">
-        <v>9.050000000000001</v>
+        <v>93.47999999999999</v>
       </c>
       <c r="N2">
-        <v>0.02176003847078625</v>
+        <v>0.08442156597128149</v>
       </c>
       <c r="O2">
-        <v>0.3220640569395018</v>
+        <v>1.24474034620506</v>
       </c>
       <c r="P2">
-        <v>9.050000000000001</v>
+        <v>81.97999999999999</v>
       </c>
       <c r="Q2">
-        <v>0.02176003847078625</v>
+        <v>0.07403594328546916</v>
       </c>
       <c r="R2">
-        <v>0.3220640569395018</v>
+        <v>1.091611185086551</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1230209670517758</v>
       </c>
       <c r="U2">
-        <v>65.59999999999999</v>
+        <v>112.7</v>
       </c>
       <c r="V2">
-        <v>0.1577302236114451</v>
+        <v>0.1017791023209609</v>
       </c>
       <c r="W2">
-        <v>0.06714202908083354</v>
+        <v>0.0505804311774461</v>
       </c>
       <c r="X2">
-        <v>0.06612528773726495</v>
+        <v>0.09615631790009899</v>
       </c>
       <c r="Y2">
-        <v>0.001016741343568592</v>
+        <v>-0.04557588672265288</v>
       </c>
       <c r="Z2">
-        <v>1.912556674258711</v>
+        <v>2.968250792565338</v>
       </c>
       <c r="AA2">
-        <v>-0.03114648881039157</v>
+        <v>-0.009963760727018319</v>
       </c>
       <c r="AB2">
-        <v>0.0573952655538036</v>
+        <v>0.09071935899746886</v>
       </c>
       <c r="AC2">
-        <v>-0.08854175436419517</v>
+        <v>-0.1006831197244872</v>
       </c>
       <c r="AD2">
-        <v>110.1</v>
+        <v>211</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.01498929520230821</v>
       </c>
       <c r="AF2">
-        <v>110.1</v>
+        <v>211.0149892952023</v>
       </c>
       <c r="AG2">
-        <v>44.5</v>
+        <v>98.31498929520232</v>
       </c>
       <c r="AH2">
-        <v>0.2093155893536122</v>
+        <v>0.1600641660063466</v>
       </c>
       <c r="AI2">
-        <v>0.189696760854583</v>
+        <v>0.25502920786454</v>
       </c>
       <c r="AJ2">
-        <v>0.09665508253692442</v>
+        <v>0.08154758373788706</v>
       </c>
       <c r="AK2">
-        <v>0.08644133644133645</v>
+        <v>0.1375583145277995</v>
       </c>
       <c r="AL2">
-        <v>1.64</v>
+        <v>3.95</v>
       </c>
       <c r="AM2">
-        <v>-6.05</v>
+        <v>-2.989999999999999</v>
       </c>
       <c r="AN2">
-        <v>25.45076282940361</v>
+        <v>2.60089243892217</v>
       </c>
       <c r="AO2">
-        <v>-8.067073170731708</v>
+        <v>12.36455696202532</v>
       </c>
       <c r="AP2">
-        <v>10.28663892741563</v>
+        <v>1.211880153036047</v>
       </c>
       <c r="AQ2">
-        <v>2.186776859504132</v>
+        <v>-16.33444816053512</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +715,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oula Fuel Marketing Company - KSCP (KWSE:OULAFUEL)</t>
+          <t>Ali Al-Ghanim Sons Automotive Company K.S.C. (Closed) (KWSE:ALG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,122 +723,110 @@
           <t>Retail (Automotive)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.0575</v>
-      </c>
-      <c r="E3">
-        <v>0.00736</v>
-      </c>
       <c r="G3">
-        <v>0.001391654310527431</v>
+        <v>0.1156462585034014</v>
       </c>
       <c r="H3">
-        <v>0.001391654310527431</v>
+        <v>0.1156462585034014</v>
       </c>
       <c r="I3">
-        <v>-0.008599872908282142</v>
+        <v>0.1013657808145117</v>
       </c>
       <c r="J3">
-        <v>-0.00853696108633565</v>
+        <v>0.1003521230063665</v>
       </c>
       <c r="K3">
-        <v>14.8</v>
+        <v>52.6</v>
       </c>
       <c r="L3">
-        <v>0.0313492904045753</v>
+        <v>0.09174952032094891</v>
       </c>
       <c r="M3">
-        <v>4.43</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="N3">
-        <v>0.02123681687440077</v>
+        <v>0.1127328329163192</v>
       </c>
       <c r="O3">
-        <v>0.2993243243243243</v>
+        <v>1.541825095057034</v>
       </c>
       <c r="P3">
-        <v>4.43</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.02123681687440077</v>
+        <v>0.09674728940783986</v>
       </c>
       <c r="R3">
-        <v>0.2993243243243243</v>
+        <v>1.32319391634981</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.1418002466091245</v>
       </c>
       <c r="U3">
-        <v>23.6</v>
+        <v>62.6</v>
       </c>
       <c r="V3">
-        <v>0.1131351869606903</v>
-      </c>
-      <c r="W3">
-        <v>0.07067812798471824</v>
+        <v>0.08701695857659161</v>
       </c>
       <c r="X3">
-        <v>0.07547403829354976</v>
-      </c>
-      <c r="Y3">
-        <v>-0.004795910308831516</v>
+        <v>0.09615631790009899</v>
       </c>
       <c r="Z3">
-        <v>1.666490169084683</v>
+        <v>38247.29530389908</v>
       </c>
       <c r="AA3">
-        <v>-0.01422676172423686</v>
+        <v>3838.197282997706</v>
       </c>
       <c r="AB3">
-        <v>0.05801399392662707</v>
+        <v>0.0916036872849281</v>
       </c>
       <c r="AC3">
-        <v>-0.07224075565086392</v>
+        <v>3838.105679310421</v>
       </c>
       <c r="AD3">
-        <v>110.1</v>
+        <v>95.5</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>0.01498929520230821</v>
       </c>
       <c r="AF3">
-        <v>110.1</v>
+        <v>95.51498929520231</v>
       </c>
       <c r="AG3">
-        <v>86.5</v>
+        <v>32.91498929520231</v>
       </c>
       <c r="AH3">
-        <v>0.3454659554439912</v>
+        <v>0.1172085316258701</v>
       </c>
       <c r="AI3">
-        <v>0.3134073441502989</v>
+        <v>0.3270893371800335</v>
       </c>
       <c r="AJ3">
-        <v>0.2931209759403592</v>
+        <v>0.04375160639300613</v>
       </c>
       <c r="AK3">
-        <v>0.2639609398840403</v>
+        <v>0.1434735777131309</v>
       </c>
       <c r="AL3">
-        <v>1.64</v>
+        <v>2.87</v>
       </c>
       <c r="AM3">
-        <v>0.49</v>
+        <v>2.87</v>
       </c>
       <c r="AN3">
-        <v>22.88981288981289</v>
+        <v>1.279886351452772</v>
       </c>
       <c r="AO3">
-        <v>-2.475609756097561</v>
+        <v>20.24390243902439</v>
       </c>
       <c r="AP3">
-        <v>17.98336798336798</v>
+        <v>0.441125084367995</v>
       </c>
       <c r="AQ3">
-        <v>-8.285714285714285</v>
+        <v>20.24390243902439</v>
       </c>
     </row>
     <row r="4">
@@ -847,127 +837,8973 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Oula Fuel Marketing Company - KSCP (KWSE:OULAFUEL)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Retail (Automotive)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.00805</v>
+      </c>
+      <c r="E4">
+        <v>0.0097</v>
+      </c>
+      <c r="G4">
+        <v>0.008762991644589362</v>
+      </c>
+      <c r="H4">
+        <v>0.008762991644589362</v>
+      </c>
+      <c r="I4">
+        <v>-0.006704707560627675</v>
+      </c>
+      <c r="J4">
+        <v>-0.006654013430291222</v>
+      </c>
+      <c r="K4">
+        <v>12.2</v>
+      </c>
+      <c r="L4">
+        <v>0.02486244141023028</v>
+      </c>
+      <c r="M4">
+        <v>7.79</v>
+      </c>
+      <c r="N4">
+        <v>0.04072138003136435</v>
+      </c>
+      <c r="O4">
+        <v>0.6385245901639345</v>
+      </c>
+      <c r="P4">
+        <v>7.79</v>
+      </c>
+      <c r="Q4">
+        <v>0.04072138003136435</v>
+      </c>
+      <c r="R4">
+        <v>0.6385245901639345</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>21.7</v>
+      </c>
+      <c r="V4">
+        <v>0.1134343962362781</v>
+      </c>
+      <c r="W4">
+        <v>0.0505804311774461</v>
+      </c>
+      <c r="X4">
+        <v>0.1167899880156609</v>
+      </c>
+      <c r="Y4">
+        <v>-0.06620955683821475</v>
+      </c>
+      <c r="Z4">
+        <v>1.49740616417455</v>
+      </c>
+      <c r="AA4">
+        <v>-0.009963760727018319</v>
+      </c>
+      <c r="AB4">
+        <v>0.09071935899746886</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1006831197244872</v>
+      </c>
+      <c r="AD4">
+        <v>115.5</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>115.5</v>
+      </c>
+      <c r="AG4">
+        <v>93.8</v>
+      </c>
+      <c r="AH4">
+        <v>0.3764667535853977</v>
+      </c>
+      <c r="AI4">
+        <v>0.3591417910447761</v>
+      </c>
+      <c r="AJ4">
+        <v>0.3290073658365485</v>
+      </c>
+      <c r="AK4">
+        <v>0.3127709236412137</v>
+      </c>
+      <c r="AL4">
+        <v>1.08</v>
+      </c>
+      <c r="AM4">
+        <v>-0.1099999999999999</v>
+      </c>
+      <c r="AN4">
+        <v>25.32894736842105</v>
+      </c>
+      <c r="AO4">
+        <v>-3.046296296296296</v>
+      </c>
+      <c r="AP4">
+        <v>20.57017543859649</v>
+      </c>
+      <c r="AQ4">
+        <v>29.90909090909094</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Al Soor Fuel Marketing Company K.S.C.P. (KWSE:SOOR)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Retail (Automotive)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>-0.00772</v>
+      </c>
+      <c r="E5">
+        <v>-0.0215</v>
+      </c>
+      <c r="G5">
+        <v>0.0003404438698556345</v>
+      </c>
+      <c r="H5">
+        <v>0.0003404438698556345</v>
+      </c>
+      <c r="I5">
+        <v>-0.01286360698125404</v>
+      </c>
+      <c r="J5">
+        <v>-0.01272754959972154</v>
+      </c>
+      <c r="K5">
+        <v>10.3</v>
+      </c>
+      <c r="L5">
+        <v>0.02219349278172808</v>
+      </c>
+      <c r="M5">
+        <v>4.59</v>
+      </c>
+      <c r="N5">
+        <v>0.0233468972533062</v>
+      </c>
+      <c r="O5">
+        <v>0.445631067961165</v>
+      </c>
+      <c r="P5">
+        <v>4.59</v>
+      </c>
+      <c r="Q5">
+        <v>0.0233468972533062</v>
+      </c>
+      <c r="R5">
+        <v>0.445631067961165</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>28.4</v>
+      </c>
+      <c r="V5">
+        <v>0.1444557477110885</v>
+      </c>
+      <c r="W5">
+        <v>0.04495853339153209</v>
+      </c>
+      <c r="X5">
+        <v>0.09033980380825951</v>
+      </c>
+      <c r="Y5">
+        <v>-0.04538127041672742</v>
+      </c>
+      <c r="Z5">
+        <v>2.480491715660075</v>
+      </c>
+      <c r="AA5">
+        <v>-0.03157058134276199</v>
+      </c>
+      <c r="AB5">
+        <v>0.09033980380825951</v>
+      </c>
+      <c r="AC5">
+        <v>-0.1219103851510215</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>-28.4</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.16884661117717</v>
+      </c>
+      <c r="AK5">
+        <v>-0.1531823085221143</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>-5.75</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>-14.56410256410256</v>
+      </c>
+      <c r="AQ5">
+        <v>1.038260869565217</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ali Al-Ghanim Sons Automotive Company K.S.C. (Closed) (KWSE:ALG)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KWSE:ALG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Retail (Automotive)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.11720853162587</v>
+      </c>
+      <c r="F2">
+        <v>0.12</v>
+      </c>
+      <c r="G2">
+        <v>719.4</v>
+      </c>
+      <c r="H2">
+        <v>746.659838302456</v>
+      </c>
+      <c r="I2">
+        <v>752.3149892952021</v>
+      </c>
+      <c r="J2">
+        <v>781.84963701788</v>
+      </c>
+      <c r="K2">
+        <v>95.5149892952023</v>
+      </c>
+      <c r="L2">
+        <v>97.7897987154243</v>
+      </c>
+      <c r="M2">
+        <v>0.0916036872849281</v>
+      </c>
+      <c r="N2">
+        <v>0.0894174873397108</v>
+      </c>
+      <c r="O2">
+        <v>0.0573141743119266</v>
+      </c>
+      <c r="P2">
+        <v>0.038845</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.096156317900099</v>
+      </c>
+      <c r="T2">
+        <v>0.0963137356133078</v>
+      </c>
+      <c r="U2">
+        <v>0.804279716208872</v>
+      </c>
+      <c r="V2">
+        <v>0.80648710814652</v>
+      </c>
+      <c r="W2">
+        <v>13.00426954791499</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>719.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.07131389334354851</v>
+      </c>
+      <c r="AC2">
+        <v>0.06742844036697249</v>
+      </c>
+      <c r="AD2">
+        <v>0.15</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>74.616</v>
+      </c>
+      <c r="AH2">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="AI2">
+        <v>23.77999999999999</v>
+      </c>
+      <c r="AJ2">
+        <v>95.51498929520231</v>
+      </c>
+      <c r="AK2">
+        <v>95.5</v>
+      </c>
+      <c r="AL2">
+        <v>2.87</v>
+      </c>
+      <c r="AM2">
+        <v>95.5</v>
+      </c>
+      <c r="AN2">
+        <v>62.6</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09033980380825951</v>
+      </c>
+      <c r="C2">
+        <v>831.7113397644489</v>
+      </c>
+      <c r="D2">
+        <v>769.1113397644489</v>
+      </c>
+      <c r="E2">
+        <v>-95.51498929520231</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>62.6</v>
+      </c>
+      <c r="H2">
+        <v>719.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>74.616</v>
+      </c>
+      <c r="K2">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L2">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="O2">
+        <v>8.717400000000003</v>
+      </c>
+      <c r="P2">
+        <v>49.3986</v>
+      </c>
+      <c r="Q2">
+        <v>65.89859999999999</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09033980380825951</v>
+      </c>
+      <c r="T2">
+        <v>0.7227175714551295</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.038845</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09026294410254711</v>
+      </c>
+      <c r="C3">
+        <v>824.607839422384</v>
+      </c>
+      <c r="D3">
+        <v>770.156989315336</v>
+      </c>
+      <c r="E3">
+        <v>-87.36583940225029</v>
+      </c>
+      <c r="F3">
+        <v>8.149149892952023</v>
+      </c>
+      <c r="G3">
+        <v>62.6</v>
+      </c>
+      <c r="H3">
+        <v>719.4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>74.616</v>
+      </c>
+      <c r="K3">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L3">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M3">
+        <v>0.3724161501079075</v>
+      </c>
+      <c r="N3">
+        <v>57.7435838498921</v>
+      </c>
+      <c r="O3">
+        <v>8.661537577483816</v>
+      </c>
+      <c r="P3">
+        <v>49.08204627240828</v>
+      </c>
+      <c r="Q3">
+        <v>65.58204627240826</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09078231727530012</v>
+      </c>
+      <c r="T3">
+        <v>0.7289227223211583</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.15</v>
+      </c>
+      <c r="W3">
+        <v>0.038845</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>156.0512345749799</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09018608439683475</v>
+      </c>
+      <c r="C4">
+        <v>817.5071861883126</v>
+      </c>
       <c r="D4">
-        <v>0.0414</v>
+        <v>771.2054859742167</v>
       </c>
       <c r="E4">
-        <v>0.0331</v>
+        <v>-79.21668950929826</v>
+      </c>
+      <c r="F4">
+        <v>16.29829978590405</v>
       </c>
       <c r="G4">
-        <v>-0.006121013133208255</v>
+        <v>62.6</v>
       </c>
       <c r="H4">
-        <v>-0.006121013133208255</v>
+        <v>719.4</v>
       </c>
       <c r="I4">
-        <v>-0.02150562851782364</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>-0.02102333317238715</v>
+        <v>74.616</v>
       </c>
       <c r="K4">
-        <v>13.3</v>
+        <v>16.49999999999999</v>
       </c>
       <c r="L4">
-        <v>0.03119136960600375</v>
+        <v>58.11600000000001</v>
       </c>
       <c r="M4">
-        <v>4.62</v>
+        <v>0.7448323002158149</v>
       </c>
       <c r="N4">
-        <v>0.02228654124457308</v>
+        <v>57.37116769978419</v>
       </c>
       <c r="O4">
-        <v>0.3473684210526315</v>
+        <v>8.605675154967631</v>
       </c>
       <c r="P4">
-        <v>4.62</v>
+        <v>48.76549254481657</v>
       </c>
       <c r="Q4">
-        <v>0.02228654124457308</v>
+        <v>65.26549254481657</v>
       </c>
       <c r="R4">
-        <v>0.3473684210526315</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.09123386162942321</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.7352545089191471</v>
       </c>
       <c r="U4">
-        <v>42</v>
+        <v>0.0457</v>
       </c>
       <c r="V4">
-        <v>0.2026049204052098</v>
+        <v>0.15</v>
       </c>
       <c r="W4">
-        <v>0.06360593017694884</v>
-      </c>
-      <c r="X4">
-        <v>0.05677653718098014</v>
+        <v>0.038845</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y4">
-        <v>0.0068293929959687</v>
+        <v>78.02561728748998</v>
       </c>
       <c r="Z4">
-        <v>2.286327077747989</v>
-      </c>
-      <c r="AA4">
-        <v>-0.04806621589654628</v>
-      </c>
-      <c r="AB4">
-        <v>0.05677653718098014</v>
-      </c>
-      <c r="AC4">
-        <v>-0.1048427530775264</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>-42</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.2540834845735027</v>
-      </c>
-      <c r="AK4">
-        <v>-0.2244788882950294</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>-6.54</v>
-      </c>
-      <c r="AN4">
-        <v>-0</v>
-      </c>
-      <c r="AP4">
-        <v>86.77685950413223</v>
-      </c>
-      <c r="AQ4">
-        <v>1.402140672782875</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09010922469112233</v>
+      </c>
+      <c r="C5">
+        <v>810.4093917063014</v>
+      </c>
+      <c r="D5">
+        <v>772.2568413851575</v>
+      </c>
+      <c r="E5">
+        <v>-71.06753961634624</v>
+      </c>
+      <c r="F5">
+        <v>24.44744967885607</v>
+      </c>
+      <c r="G5">
+        <v>62.6</v>
+      </c>
+      <c r="H5">
+        <v>719.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>74.616</v>
+      </c>
+      <c r="K5">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L5">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M5">
+        <v>1.117248450323722</v>
+      </c>
+      <c r="N5">
+        <v>56.99875154967629</v>
+      </c>
+      <c r="O5">
+        <v>8.549812732451445</v>
+      </c>
+      <c r="P5">
+        <v>48.44893881722484</v>
+      </c>
+      <c r="Q5">
+        <v>64.94893881722484</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09169471617641478</v>
+      </c>
+      <c r="T5">
+        <v>0.7417168478181251</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.15</v>
+      </c>
+      <c r="W5">
+        <v>0.038845</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>52.01707819165998</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09003236498540994</v>
+      </c>
+      <c r="C6">
+        <v>803.3144676839973</v>
+      </c>
+      <c r="D6">
+        <v>773.3110672558054</v>
+      </c>
+      <c r="E6">
+        <v>-62.91838972339422</v>
+      </c>
+      <c r="F6">
+        <v>32.59659957180809</v>
+      </c>
+      <c r="G6">
+        <v>62.6</v>
+      </c>
+      <c r="H6">
+        <v>719.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>74.616</v>
+      </c>
+      <c r="K6">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L6">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M6">
+        <v>1.48966460043163</v>
+      </c>
+      <c r="N6">
+        <v>56.62633539956838</v>
+      </c>
+      <c r="O6">
+        <v>8.493950309935258</v>
+      </c>
+      <c r="P6">
+        <v>48.13238508963312</v>
+      </c>
+      <c r="Q6">
+        <v>64.63238508963312</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09216517185980203</v>
+      </c>
+      <c r="T6">
+        <v>0.7483138187774987</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.15</v>
+      </c>
+      <c r="W6">
+        <v>0.038845</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>39.01280864374498</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08995550527969756</v>
+      </c>
+      <c r="C7">
+        <v>796.222425893065</v>
+      </c>
+      <c r="D7">
+        <v>774.3681753578251</v>
+      </c>
+      <c r="E7">
+        <v>-54.7692398304422</v>
+      </c>
+      <c r="F7">
+        <v>40.74574946476012</v>
+      </c>
+      <c r="G7">
+        <v>62.6</v>
+      </c>
+      <c r="H7">
+        <v>719.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>74.616</v>
+      </c>
+      <c r="K7">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L7">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M7">
+        <v>1.862080750539538</v>
+      </c>
+      <c r="N7">
+        <v>56.25391924946047</v>
+      </c>
+      <c r="O7">
+        <v>8.438087887419071</v>
+      </c>
+      <c r="P7">
+        <v>47.81583136204139</v>
+      </c>
+      <c r="Q7">
+        <v>64.31583136204139</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09264553187336586</v>
+      </c>
+      <c r="T7">
+        <v>0.7550496733360169</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.038845</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>31.21024691499598</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08987864557398517</v>
+      </c>
+      <c r="C8">
+        <v>789.1332781696248</v>
+      </c>
+      <c r="D8">
+        <v>775.4281775273369</v>
+      </c>
+      <c r="E8">
+        <v>-46.62008993749018</v>
+      </c>
+      <c r="F8">
+        <v>48.89489935771213</v>
+      </c>
+      <c r="G8">
+        <v>62.6</v>
+      </c>
+      <c r="H8">
+        <v>719.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>74.616</v>
+      </c>
+      <c r="K8">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L8">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M8">
+        <v>2.234496900647445</v>
+      </c>
+      <c r="N8">
+        <v>55.88150309935256</v>
+      </c>
+      <c r="O8">
+        <v>8.382225464902886</v>
+      </c>
+      <c r="P8">
+        <v>47.49927763444968</v>
+      </c>
+      <c r="Q8">
+        <v>63.99927763444967</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09313611231275018</v>
+      </c>
+      <c r="T8">
+        <v>0.7619288439489715</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.15</v>
+      </c>
+      <c r="W8">
+        <v>0.038845</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>26.00853909582999</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08980178586827278</v>
+      </c>
+      <c r="C9">
+        <v>782.0470364146933</v>
+      </c>
+      <c r="D9">
+        <v>776.4910856653574</v>
+      </c>
+      <c r="E9">
+        <v>-38.47094004453815</v>
+      </c>
+      <c r="F9">
+        <v>57.04404925066417</v>
+      </c>
+      <c r="G9">
+        <v>62.6</v>
+      </c>
+      <c r="H9">
+        <v>719.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>74.616</v>
+      </c>
+      <c r="K9">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L9">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M9">
+        <v>2.606913050755353</v>
+      </c>
+      <c r="N9">
+        <v>55.50908694924465</v>
+      </c>
+      <c r="O9">
+        <v>8.326363042386699</v>
+      </c>
+      <c r="P9">
+        <v>47.18272390685796</v>
+      </c>
+      <c r="Q9">
+        <v>63.68272390685795</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09363724286911052</v>
+      </c>
+      <c r="T9">
+        <v>0.7689559537148931</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.15</v>
+      </c>
+      <c r="W9">
+        <v>0.038845</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>22.29303351071141</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08972492616256041</v>
+      </c>
+      <c r="C10">
+        <v>774.9637125946291</v>
+      </c>
+      <c r="D10">
+        <v>777.5569117382453</v>
+      </c>
+      <c r="E10">
+        <v>-30.32179015158613</v>
+      </c>
+      <c r="F10">
+        <v>65.19319914361618</v>
+      </c>
+      <c r="G10">
+        <v>62.6</v>
+      </c>
+      <c r="H10">
+        <v>719.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>74.616</v>
+      </c>
+      <c r="K10">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L10">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M10">
+        <v>2.97932920086326</v>
+      </c>
+      <c r="N10">
+        <v>55.13667079913674</v>
+      </c>
+      <c r="O10">
+        <v>8.270500619870512</v>
+      </c>
+      <c r="P10">
+        <v>46.86617017926623</v>
+      </c>
+      <c r="Q10">
+        <v>63.36617017926623</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09414926756800043</v>
+      </c>
+      <c r="T10">
+        <v>0.7761358267365956</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.15</v>
+      </c>
+      <c r="W10">
+        <v>0.038845</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>19.50640432187249</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.089648066456848</v>
+      </c>
+      <c r="C11">
+        <v>767.8833187415829</v>
+      </c>
+      <c r="D11">
+        <v>778.6256677781511</v>
+      </c>
+      <c r="E11">
+        <v>-22.1726402586341</v>
+      </c>
+      <c r="F11">
+        <v>73.34234903656821</v>
+      </c>
+      <c r="G11">
+        <v>62.6</v>
+      </c>
+      <c r="H11">
+        <v>719.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>74.616</v>
+      </c>
+      <c r="K11">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L11">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M11">
+        <v>3.351745350971167</v>
+      </c>
+      <c r="N11">
+        <v>54.76425464902884</v>
+      </c>
+      <c r="O11">
+        <v>8.214638197354327</v>
+      </c>
+      <c r="P11">
+        <v>46.54961645167452</v>
+      </c>
+      <c r="Q11">
+        <v>63.04961645167451</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09467254555697582</v>
+      </c>
+      <c r="T11">
+        <v>0.7834734991653683</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.15</v>
+      </c>
+      <c r="W11">
+        <v>0.038845</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>17.33902606388666</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08957120675113561</v>
+      </c>
+      <c r="C12">
+        <v>760.8058669539485</v>
+      </c>
+      <c r="D12">
+        <v>779.6973658834687</v>
+      </c>
+      <c r="E12">
+        <v>-14.02349036568208</v>
+      </c>
+      <c r="F12">
+        <v>81.49149892952023</v>
+      </c>
+      <c r="G12">
+        <v>62.6</v>
+      </c>
+      <c r="H12">
+        <v>719.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>74.616</v>
+      </c>
+      <c r="K12">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L12">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M12">
+        <v>3.724161501079075</v>
+      </c>
+      <c r="N12">
+        <v>54.39183849892093</v>
+      </c>
+      <c r="O12">
+        <v>8.158775774838141</v>
+      </c>
+      <c r="P12">
+        <v>46.23306272408279</v>
+      </c>
+      <c r="Q12">
+        <v>62.73306272408279</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09520745194570623</v>
+      </c>
+      <c r="T12">
+        <v>0.7909742309814474</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.15</v>
+      </c>
+      <c r="W12">
+        <v>0.038845</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>15.60512345749799</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08949434704542321</v>
+      </c>
+      <c r="C13">
+        <v>753.7313693968212</v>
+      </c>
+      <c r="D13">
+        <v>780.7720182192934</v>
+      </c>
+      <c r="E13">
+        <v>-5.874340472730054</v>
+      </c>
+      <c r="F13">
+        <v>89.64064882247226</v>
+      </c>
+      <c r="G13">
+        <v>62.6</v>
+      </c>
+      <c r="H13">
+        <v>719.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>74.616</v>
+      </c>
+      <c r="K13">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L13">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M13">
+        <v>4.096577651186982</v>
+      </c>
+      <c r="N13">
+        <v>54.01942234881302</v>
+      </c>
+      <c r="O13">
+        <v>8.102913352321954</v>
+      </c>
+      <c r="P13">
+        <v>45.91650899649107</v>
+      </c>
+      <c r="Q13">
+        <v>62.41650899649106</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09575437870272271</v>
+      </c>
+      <c r="T13">
+        <v>0.798643518568674</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.15</v>
+      </c>
+      <c r="W13">
+        <v>0.038845</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>14.18647587045272</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08941748733971085</v>
+      </c>
+      <c r="C14">
+        <v>746.6598383024558</v>
+      </c>
+      <c r="D14">
+        <v>781.84963701788</v>
+      </c>
+      <c r="E14">
+        <v>2.274809420221956</v>
+      </c>
+      <c r="F14">
+        <v>97.78979871542427</v>
+      </c>
+      <c r="G14">
+        <v>62.6</v>
+      </c>
+      <c r="H14">
+        <v>719.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>74.616</v>
+      </c>
+      <c r="K14">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L14">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M14">
+        <v>4.468993801294889</v>
+      </c>
+      <c r="N14">
+        <v>53.64700619870511</v>
+      </c>
+      <c r="O14">
+        <v>8.047050929805769</v>
+      </c>
+      <c r="P14">
+        <v>45.59995526889934</v>
+      </c>
+      <c r="Q14">
+        <v>62.09995526889934</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09631373561330778</v>
+      </c>
+      <c r="T14">
+        <v>0.8064871081465196</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.15</v>
+      </c>
+      <c r="W14">
+        <v>0.038845</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>13.00426954791499</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08951742763399845</v>
+      </c>
+      <c r="C15">
+        <v>737.110045747116</v>
+      </c>
+      <c r="D15">
+        <v>780.4489943554923</v>
+      </c>
+      <c r="E15">
+        <v>10.423959313174</v>
+      </c>
+      <c r="F15">
+        <v>105.9389486083763</v>
+      </c>
+      <c r="G15">
+        <v>62.6</v>
+      </c>
+      <c r="H15">
+        <v>719.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>74.616</v>
+      </c>
+      <c r="K15">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L15">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M15">
+        <v>5.0109122691762</v>
+      </c>
+      <c r="N15">
+        <v>53.1050877308238</v>
+      </c>
+      <c r="O15">
+        <v>7.965763159623572</v>
+      </c>
+      <c r="P15">
+        <v>45.13932457120023</v>
+      </c>
+      <c r="Q15">
+        <v>61.63932457120023</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09688595130344649</v>
+      </c>
+      <c r="T15">
+        <v>0.8145110101284534</v>
+      </c>
+      <c r="U15">
+        <v>0.0473</v>
+      </c>
+      <c r="V15">
+        <v>0.15</v>
+      </c>
+      <c r="W15">
+        <v>0.040205</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>11.59788814453827</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08945416792828605</v>
+      </c>
+      <c r="C16">
+        <v>729.8468840263671</v>
+      </c>
+      <c r="D16">
+        <v>781.3349825276954</v>
+      </c>
+      <c r="E16">
+        <v>18.57310920612602</v>
+      </c>
+      <c r="F16">
+        <v>114.0880985013283</v>
+      </c>
+      <c r="G16">
+        <v>62.6</v>
+      </c>
+      <c r="H16">
+        <v>719.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>74.616</v>
+      </c>
+      <c r="K16">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L16">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M16">
+        <v>5.39636705911283</v>
+      </c>
+      <c r="N16">
+        <v>52.71963294088718</v>
+      </c>
+      <c r="O16">
+        <v>7.907944941133079</v>
+      </c>
+      <c r="P16">
+        <v>44.8116879997541</v>
+      </c>
+      <c r="Q16">
+        <v>61.31168799975409</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09747147433521633</v>
+      </c>
+      <c r="T16">
+        <v>0.8227215144820601</v>
+      </c>
+      <c r="U16">
+        <v>0.0473</v>
+      </c>
+      <c r="V16">
+        <v>0.15</v>
+      </c>
+      <c r="W16">
+        <v>0.040205</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>10.76946756278554</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08987540822257367</v>
+      </c>
+      <c r="C17">
+        <v>715.8356404028541</v>
+      </c>
+      <c r="D17">
+        <v>775.4728887971344</v>
+      </c>
+      <c r="E17">
+        <v>26.72225909907803</v>
+      </c>
+      <c r="F17">
+        <v>122.2372483942803</v>
+      </c>
+      <c r="G17">
+        <v>62.6</v>
+      </c>
+      <c r="H17">
+        <v>719.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>74.616</v>
+      </c>
+      <c r="K17">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L17">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M17">
+        <v>6.246323392947725</v>
+      </c>
+      <c r="N17">
+        <v>51.86967660705228</v>
+      </c>
+      <c r="O17">
+        <v>7.780451491057844</v>
+      </c>
+      <c r="P17">
+        <v>44.08922511599444</v>
+      </c>
+      <c r="Q17">
+        <v>60.58922511599443</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09807077437949843</v>
+      </c>
+      <c r="T17">
+        <v>0.8311252071733989</v>
+      </c>
+      <c r="U17">
+        <v>0.0511</v>
+      </c>
+      <c r="V17">
+        <v>0.15</v>
+      </c>
+      <c r="W17">
+        <v>0.043435</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>9.304033163831161</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08984444851686128</v>
+      </c>
+      <c r="C18">
+        <v>708.1143375866134</v>
+      </c>
+      <c r="D18">
+        <v>775.9007358738457</v>
+      </c>
+      <c r="E18">
+        <v>34.87140899203006</v>
+      </c>
+      <c r="F18">
+        <v>130.3863982872324</v>
+      </c>
+      <c r="G18">
+        <v>62.6</v>
+      </c>
+      <c r="H18">
+        <v>719.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>74.616</v>
+      </c>
+      <c r="K18">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L18">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M18">
+        <v>6.662744952477574</v>
+      </c>
+      <c r="N18">
+        <v>51.45325504752243</v>
+      </c>
+      <c r="O18">
+        <v>7.717988257128366</v>
+      </c>
+      <c r="P18">
+        <v>43.73526679039406</v>
+      </c>
+      <c r="Q18">
+        <v>60.23526679039406</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09868434347245392</v>
+      </c>
+      <c r="T18">
+        <v>0.8397289877859601</v>
+      </c>
+      <c r="U18">
+        <v>0.0511</v>
+      </c>
+      <c r="V18">
+        <v>0.15</v>
+      </c>
+      <c r="W18">
+        <v>0.043435</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>8.72253109109171</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08981348881114889</v>
+      </c>
+      <c r="C19">
+        <v>700.3935071380706</v>
+      </c>
+      <c r="D19">
+        <v>776.329055318255</v>
+      </c>
+      <c r="E19">
+        <v>43.02055888498209</v>
+      </c>
+      <c r="F19">
+        <v>138.5355481801844</v>
+      </c>
+      <c r="G19">
+        <v>62.6</v>
+      </c>
+      <c r="H19">
+        <v>719.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>74.616</v>
+      </c>
+      <c r="K19">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L19">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M19">
+        <v>7.079166512007423</v>
+      </c>
+      <c r="N19">
+        <v>51.03683348799258</v>
+      </c>
+      <c r="O19">
+        <v>7.655525023198888</v>
+      </c>
+      <c r="P19">
+        <v>43.38130846479369</v>
+      </c>
+      <c r="Q19">
+        <v>59.88130846479368</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09931269736282999</v>
+      </c>
+      <c r="T19">
+        <v>0.8485400884132815</v>
+      </c>
+      <c r="U19">
+        <v>0.0511</v>
+      </c>
+      <c r="V19">
+        <v>0.15</v>
+      </c>
+      <c r="W19">
+        <v>0.043435</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>8.209441026909845</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09007322910543651</v>
+      </c>
+      <c r="C20">
+        <v>688.6655091804814</v>
+      </c>
+      <c r="D20">
+        <v>772.7502072536178</v>
+      </c>
+      <c r="E20">
+        <v>51.1697087779341</v>
+      </c>
+      <c r="F20">
+        <v>146.6846980731364</v>
+      </c>
+      <c r="G20">
+        <v>62.6</v>
+      </c>
+      <c r="H20">
+        <v>719.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>74.616</v>
+      </c>
+      <c r="K20">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L20">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M20">
+        <v>7.774288997876231</v>
+      </c>
+      <c r="N20">
+        <v>50.34171100212377</v>
+      </c>
+      <c r="O20">
+        <v>7.551256650318567</v>
+      </c>
+      <c r="P20">
+        <v>42.79045435180521</v>
+      </c>
+      <c r="Q20">
+        <v>59.2904543518052</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.0999563769578494</v>
+      </c>
+      <c r="T20">
+        <v>0.8575660939339524</v>
+      </c>
+      <c r="U20">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0.15</v>
+      </c>
+      <c r="W20">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>7.475410293581323</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09005841939972412</v>
+      </c>
+      <c r="C21">
+        <v>680.7195284637746</v>
+      </c>
+      <c r="D21">
+        <v>772.9533764298631</v>
+      </c>
+      <c r="E21">
+        <v>59.31885867088612</v>
+      </c>
+      <c r="F21">
+        <v>154.8338479660884</v>
+      </c>
+      <c r="G21">
+        <v>62.6</v>
+      </c>
+      <c r="H21">
+        <v>719.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>74.616</v>
+      </c>
+      <c r="K21">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L21">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M21">
+        <v>8.206193942202688</v>
+      </c>
+      <c r="N21">
+        <v>49.90980605779732</v>
+      </c>
+      <c r="O21">
+        <v>7.486470908669599</v>
+      </c>
+      <c r="P21">
+        <v>42.42333514912772</v>
+      </c>
+      <c r="Q21">
+        <v>58.92333514912772</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1006159498762026</v>
+      </c>
+      <c r="T21">
+        <v>0.866814963788467</v>
+      </c>
+      <c r="U21">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0.15</v>
+      </c>
+      <c r="W21">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>7.081967646550727</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09004360969401173</v>
+      </c>
+      <c r="C22">
+        <v>672.7736546084293</v>
+      </c>
+      <c r="D22">
+        <v>773.1566524674697</v>
+      </c>
+      <c r="E22">
+        <v>67.46800856383815</v>
+      </c>
+      <c r="F22">
+        <v>162.9829978590405</v>
+      </c>
+      <c r="G22">
+        <v>62.6</v>
+      </c>
+      <c r="H22">
+        <v>719.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>74.616</v>
+      </c>
+      <c r="K22">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L22">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M22">
+        <v>8.638098886529146</v>
+      </c>
+      <c r="N22">
+        <v>49.47790111347086</v>
+      </c>
+      <c r="O22">
+        <v>7.42168516702063</v>
+      </c>
+      <c r="P22">
+        <v>42.05621594645024</v>
+      </c>
+      <c r="Q22">
+        <v>58.55621594645023</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1012920121175147</v>
+      </c>
+      <c r="T22">
+        <v>0.8762950553893445</v>
+      </c>
+      <c r="U22">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V22">
+        <v>0.15</v>
+      </c>
+      <c r="W22">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>6.727869264223191</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09002879998829932</v>
+      </c>
+      <c r="C23">
+        <v>664.8278876987772</v>
+      </c>
+      <c r="D23">
+        <v>773.3600354507697</v>
+      </c>
+      <c r="E23">
+        <v>75.61715845679016</v>
+      </c>
+      <c r="F23">
+        <v>171.1321477519925</v>
+      </c>
+      <c r="G23">
+        <v>62.6</v>
+      </c>
+      <c r="H23">
+        <v>719.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>74.616</v>
+      </c>
+      <c r="K23">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L23">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M23">
+        <v>9.070003830855603</v>
+      </c>
+      <c r="N23">
+        <v>49.0459961691444</v>
+      </c>
+      <c r="O23">
+        <v>7.356899425371662</v>
+      </c>
+      <c r="P23">
+        <v>41.68909674377274</v>
+      </c>
+      <c r="Q23">
+        <v>58.18909674377273</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1019851898586067</v>
+      </c>
+      <c r="T23">
+        <v>0.8860151493092314</v>
+      </c>
+      <c r="U23">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V23">
+        <v>0.15</v>
+      </c>
+      <c r="W23">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>6.40749453735542</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.09038799028258696</v>
+      </c>
+      <c r="C24">
+        <v>651.7759287479217</v>
+      </c>
+      <c r="D24">
+        <v>768.4572263928662</v>
+      </c>
+      <c r="E24">
+        <v>83.7663083497422</v>
+      </c>
+      <c r="F24">
+        <v>179.2812976449445</v>
+      </c>
+      <c r="G24">
+        <v>62.6</v>
+      </c>
+      <c r="H24">
+        <v>719.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>74.616</v>
+      </c>
+      <c r="K24">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L24">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M24">
+        <v>9.860471370471949</v>
+      </c>
+      <c r="N24">
+        <v>48.25552862952806</v>
+      </c>
+      <c r="O24">
+        <v>7.23832929442921</v>
+      </c>
+      <c r="P24">
+        <v>41.01719933509885</v>
+      </c>
+      <c r="Q24">
+        <v>57.51719933509884</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.102696141387932</v>
+      </c>
+      <c r="T24">
+        <v>0.8959844764065515</v>
+      </c>
+      <c r="U24">
+        <v>0.055</v>
+      </c>
+      <c r="V24">
+        <v>0.15</v>
+      </c>
+      <c r="W24">
+        <v>0.04675</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.893835884360812</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.09039018057687455</v>
+      </c>
+      <c r="C25">
+        <v>643.5970728641843</v>
+      </c>
+      <c r="D25">
+        <v>768.4275204020807</v>
+      </c>
+      <c r="E25">
+        <v>91.91545824269421</v>
+      </c>
+      <c r="F25">
+        <v>187.4304475378965</v>
+      </c>
+      <c r="G25">
+        <v>62.6</v>
+      </c>
+      <c r="H25">
+        <v>719.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>74.616</v>
+      </c>
+      <c r="K25">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L25">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M25">
+        <v>10.30867461458431</v>
+      </c>
+      <c r="N25">
+        <v>47.80732538541569</v>
+      </c>
+      <c r="O25">
+        <v>7.171098807812355</v>
+      </c>
+      <c r="P25">
+        <v>40.63622657760334</v>
+      </c>
+      <c r="Q25">
+        <v>57.13622657760333</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1034255591907462</v>
+      </c>
+      <c r="T25">
+        <v>0.9062127470648409</v>
+      </c>
+      <c r="U25">
+        <v>0.055</v>
+      </c>
+      <c r="V25">
+        <v>0.15</v>
+      </c>
+      <c r="W25">
+        <v>0.04675</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.637582150258169</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.09039237087116216</v>
+      </c>
+      <c r="C26">
+        <v>635.418219277027</v>
+      </c>
+      <c r="D26">
+        <v>768.3978167078754</v>
+      </c>
+      <c r="E26">
+        <v>100.0646081356462</v>
+      </c>
+      <c r="F26">
+        <v>195.5795974308485</v>
+      </c>
+      <c r="G26">
+        <v>62.6</v>
+      </c>
+      <c r="H26">
+        <v>719.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>74.616</v>
+      </c>
+      <c r="K26">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L26">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M26">
+        <v>10.75687785869667</v>
+      </c>
+      <c r="N26">
+        <v>47.35912214130334</v>
+      </c>
+      <c r="O26">
+        <v>7.103868321195502</v>
+      </c>
+      <c r="P26">
+        <v>40.25525382010784</v>
+      </c>
+      <c r="Q26">
+        <v>56.75525382010783</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1041741721988976</v>
+      </c>
+      <c r="T26">
+        <v>0.9167101827404537</v>
+      </c>
+      <c r="U26">
+        <v>0.055</v>
+      </c>
+      <c r="V26">
+        <v>0.15</v>
+      </c>
+      <c r="W26">
+        <v>0.04675</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>5.402682893997412</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.09039456116544978</v>
+      </c>
+      <c r="C27">
+        <v>627.239367986183</v>
+      </c>
+      <c r="D27">
+        <v>768.3681153099835</v>
+      </c>
+      <c r="E27">
+        <v>108.2137580285983</v>
+      </c>
+      <c r="F27">
+        <v>203.7287473238006</v>
+      </c>
+      <c r="G27">
+        <v>62.6</v>
+      </c>
+      <c r="H27">
+        <v>719.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>74.616</v>
+      </c>
+      <c r="K27">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L27">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M27">
+        <v>11.20508110280903</v>
+      </c>
+      <c r="N27">
+        <v>46.91091889719097</v>
+      </c>
+      <c r="O27">
+        <v>7.036637834578647</v>
+      </c>
+      <c r="P27">
+        <v>39.87428106261233</v>
+      </c>
+      <c r="Q27">
+        <v>56.37428106261232</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1049427482205997</v>
+      </c>
+      <c r="T27">
+        <v>0.9274875500340828</v>
+      </c>
+      <c r="U27">
+        <v>0.055</v>
+      </c>
+      <c r="V27">
+        <v>0.15</v>
+      </c>
+      <c r="W27">
+        <v>0.04675</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>5.186575578237515</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.09039675145973738</v>
+      </c>
+      <c r="C28">
+        <v>619.0605189913865</v>
+      </c>
+      <c r="D28">
+        <v>768.3384162081392</v>
+      </c>
+      <c r="E28">
+        <v>116.3629079215503</v>
+      </c>
+      <c r="F28">
+        <v>211.8778972167526</v>
+      </c>
+      <c r="G28">
+        <v>62.6</v>
+      </c>
+      <c r="H28">
+        <v>719.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>74.616</v>
+      </c>
+      <c r="K28">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L28">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M28">
+        <v>11.65328434692139</v>
+      </c>
+      <c r="N28">
+        <v>46.46271565307861</v>
+      </c>
+      <c r="O28">
+        <v>6.969407347961793</v>
+      </c>
+      <c r="P28">
+        <v>39.49330830511682</v>
+      </c>
+      <c r="Q28">
+        <v>55.99330830511681</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1057320965672127</v>
+      </c>
+      <c r="T28">
+        <v>0.9385561975248371</v>
+      </c>
+      <c r="U28">
+        <v>0.055</v>
+      </c>
+      <c r="V28">
+        <v>0.15</v>
+      </c>
+      <c r="W28">
+        <v>0.04675</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.987091902151456</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.09039894175402499</v>
+      </c>
+      <c r="C29">
+        <v>610.8816722923716</v>
+      </c>
+      <c r="D29">
+        <v>768.3087194020762</v>
+      </c>
+      <c r="E29">
+        <v>124.5120578145023</v>
+      </c>
+      <c r="F29">
+        <v>220.0270471097046</v>
+      </c>
+      <c r="G29">
+        <v>62.6</v>
+      </c>
+      <c r="H29">
+        <v>719.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>74.616</v>
+      </c>
+      <c r="K29">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L29">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M29">
+        <v>12.10148759103375</v>
+      </c>
+      <c r="N29">
+        <v>46.01451240896625</v>
+      </c>
+      <c r="O29">
+        <v>6.902176861344939</v>
+      </c>
+      <c r="P29">
+        <v>39.11233554762131</v>
+      </c>
+      <c r="Q29">
+        <v>55.61233554762131</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1065430708959247</v>
+      </c>
+      <c r="T29">
+        <v>0.9499280956317765</v>
+      </c>
+      <c r="U29">
+        <v>0.055</v>
+      </c>
+      <c r="V29">
+        <v>0.15</v>
+      </c>
+      <c r="W29">
+        <v>0.04675</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>4.802384794664366</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.09040113204831261</v>
+      </c>
+      <c r="C30">
+        <v>602.7028278888715</v>
+      </c>
+      <c r="D30">
+        <v>768.2790248915281</v>
+      </c>
+      <c r="E30">
+        <v>132.6612077074544</v>
+      </c>
+      <c r="F30">
+        <v>228.1761970026567</v>
+      </c>
+      <c r="G30">
+        <v>62.6</v>
+      </c>
+      <c r="H30">
+        <v>719.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>74.616</v>
+      </c>
+      <c r="K30">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L30">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M30">
+        <v>12.54969083514612</v>
+      </c>
+      <c r="N30">
+        <v>45.56630916485389</v>
+      </c>
+      <c r="O30">
+        <v>6.834946374728085</v>
+      </c>
+      <c r="P30">
+        <v>38.73136279012581</v>
+      </c>
+      <c r="Q30">
+        <v>55.2313627901258</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1073765722893231</v>
+      </c>
+      <c r="T30">
+        <v>0.9616158797972418</v>
+      </c>
+      <c r="U30">
+        <v>0.055</v>
+      </c>
+      <c r="V30">
+        <v>0.15</v>
+      </c>
+      <c r="W30">
+        <v>0.04675</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>4.630871051997781</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.09134002234260022</v>
+      </c>
+      <c r="C31">
+        <v>582.0327761185559</v>
+      </c>
+      <c r="D31">
+        <v>755.7581230141645</v>
+      </c>
+      <c r="E31">
+        <v>140.8103576004063</v>
+      </c>
+      <c r="F31">
+        <v>236.3253468956086</v>
+      </c>
+      <c r="G31">
+        <v>62.6</v>
+      </c>
+      <c r="H31">
+        <v>719.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>74.616</v>
+      </c>
+      <c r="K31">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L31">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M31">
+        <v>13.89593039746179</v>
+      </c>
+      <c r="N31">
+        <v>44.22006960253822</v>
+      </c>
+      <c r="O31">
+        <v>6.633010440380733</v>
+      </c>
+      <c r="P31">
+        <v>37.58705916215749</v>
+      </c>
+      <c r="Q31">
+        <v>54.08705916215748</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1082335525952116</v>
+      </c>
+      <c r="T31">
+        <v>0.9736328973194809</v>
+      </c>
+      <c r="U31">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V31">
+        <v>0.15</v>
+      </c>
+      <c r="W31">
+        <v>0.04998</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>4.182231656155632</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.09137451263688781</v>
+      </c>
+      <c r="C32">
+        <v>573.4314355718059</v>
+      </c>
+      <c r="D32">
+        <v>755.3059323603666</v>
+      </c>
+      <c r="E32">
+        <v>148.9595074933584</v>
+      </c>
+      <c r="F32">
+        <v>244.4744967885607</v>
+      </c>
+      <c r="G32">
+        <v>62.6</v>
+      </c>
+      <c r="H32">
+        <v>719.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>74.616</v>
+      </c>
+      <c r="K32">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L32">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M32">
+        <v>14.37510041116737</v>
+      </c>
+      <c r="N32">
+        <v>43.74089958883263</v>
+      </c>
+      <c r="O32">
+        <v>6.561134938324896</v>
+      </c>
+      <c r="P32">
+        <v>37.17976465050774</v>
+      </c>
+      <c r="Q32">
+        <v>53.67976465050773</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1091150180526969</v>
+      </c>
+      <c r="T32">
+        <v>0.9859932581994981</v>
+      </c>
+      <c r="U32">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V32">
+        <v>0.15</v>
+      </c>
+      <c r="W32">
+        <v>0.04998</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>4.042823934283777</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.09251570293117545</v>
+      </c>
+      <c r="C33">
+        <v>550.6197499772377</v>
+      </c>
+      <c r="D33">
+        <v>740.6433966587504</v>
+      </c>
+      <c r="E33">
+        <v>157.1086573863104</v>
+      </c>
+      <c r="F33">
+        <v>252.6236466815127</v>
+      </c>
+      <c r="G33">
+        <v>62.6</v>
+      </c>
+      <c r="H33">
+        <v>719.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>74.616</v>
+      </c>
+      <c r="K33">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L33">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M33">
+        <v>15.9152897409353</v>
+      </c>
+      <c r="N33">
+        <v>42.20071025906471</v>
+      </c>
+      <c r="O33">
+        <v>6.330106538859707</v>
+      </c>
+      <c r="P33">
+        <v>35.870603720205</v>
+      </c>
+      <c r="Q33">
+        <v>52.37060372020499</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1100220332335876</v>
+      </c>
+      <c r="T33">
+        <v>0.998711890409371</v>
+      </c>
+      <c r="U33">
+        <v>0.063</v>
+      </c>
+      <c r="V33">
+        <v>0.15</v>
+      </c>
+      <c r="W33">
+        <v>0.05355</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>3.651582908385347</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.09258589322546304</v>
+      </c>
+      <c r="C34">
+        <v>541.5873247626516</v>
+      </c>
+      <c r="D34">
+        <v>739.7601213371164</v>
+      </c>
+      <c r="E34">
+        <v>165.2578072792624</v>
+      </c>
+      <c r="F34">
+        <v>260.7727965744647</v>
+      </c>
+      <c r="G34">
+        <v>62.6</v>
+      </c>
+      <c r="H34">
+        <v>719.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>74.616</v>
+      </c>
+      <c r="K34">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L34">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M34">
+        <v>16.42868618419128</v>
+      </c>
+      <c r="N34">
+        <v>41.68731381580873</v>
+      </c>
+      <c r="O34">
+        <v>6.25309707237131</v>
+      </c>
+      <c r="P34">
+        <v>35.43421674343742</v>
+      </c>
+      <c r="Q34">
+        <v>51.93421674343741</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1109557253315633</v>
+      </c>
+      <c r="T34">
+        <v>1.011804600037181</v>
+      </c>
+      <c r="U34">
+        <v>0.063</v>
+      </c>
+      <c r="V34">
+        <v>0.15</v>
+      </c>
+      <c r="W34">
+        <v>0.05355</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>3.537470942498305</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.09464763351975065</v>
+      </c>
+      <c r="C35">
+        <v>508.4012094376681</v>
+      </c>
+      <c r="D35">
+        <v>714.7231559050848</v>
+      </c>
+      <c r="E35">
+        <v>173.4069571722144</v>
+      </c>
+      <c r="F35">
+        <v>268.9219464674168</v>
+      </c>
+      <c r="G35">
+        <v>62.6</v>
+      </c>
+      <c r="H35">
+        <v>719.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>74.616</v>
+      </c>
+      <c r="K35">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L35">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M35">
+        <v>18.85142844736592</v>
+      </c>
+      <c r="N35">
+        <v>39.2645715526341</v>
+      </c>
+      <c r="O35">
+        <v>5.889685732895115</v>
+      </c>
+      <c r="P35">
+        <v>33.37488581973898</v>
+      </c>
+      <c r="Q35">
+        <v>49.87488581973897</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1119172888354488</v>
+      </c>
+      <c r="T35">
+        <v>1.025288136818061</v>
+      </c>
+      <c r="U35">
+        <v>0.0701</v>
+      </c>
+      <c r="V35">
+        <v>0.15</v>
+      </c>
+      <c r="W35">
+        <v>0.05958499999999999</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>3.082843306132617</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1009338738140383</v>
+      </c>
+      <c r="C36">
+        <v>433.3969850298124</v>
+      </c>
+      <c r="D36">
+        <v>647.8680813901811</v>
+      </c>
+      <c r="E36">
+        <v>181.5561070651665</v>
+      </c>
+      <c r="F36">
+        <v>277.0710963603688</v>
+      </c>
+      <c r="G36">
+        <v>62.6</v>
+      </c>
+      <c r="H36">
+        <v>719.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>74.616</v>
+      </c>
+      <c r="K36">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L36">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M36">
+        <v>25.32429820733771</v>
+      </c>
+      <c r="N36">
+        <v>32.79170179266229</v>
+      </c>
+      <c r="O36">
+        <v>4.918755268899345</v>
+      </c>
+      <c r="P36">
+        <v>27.87294652376295</v>
+      </c>
+      <c r="Q36">
+        <v>44.37294652376294</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1129079906273307</v>
+      </c>
+      <c r="T36">
+        <v>1.039180265622603</v>
+      </c>
+      <c r="U36">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V36">
+        <v>0.15</v>
+      </c>
+      <c r="W36">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>2.294871096690881</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1012454641083259</v>
+      </c>
+      <c r="C37">
+        <v>422.2578632651295</v>
+      </c>
+      <c r="D37">
+        <v>644.8781095184503</v>
+      </c>
+      <c r="E37">
+        <v>189.7052569581185</v>
+      </c>
+      <c r="F37">
+        <v>285.2202462533209</v>
+      </c>
+      <c r="G37">
+        <v>62.6</v>
+      </c>
+      <c r="H37">
+        <v>719.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>74.616</v>
+      </c>
+      <c r="K37">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L37">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M37">
+        <v>26.06913050755353</v>
+      </c>
+      <c r="N37">
+        <v>32.04686949244648</v>
+      </c>
+      <c r="O37">
+        <v>4.807030423866972</v>
+      </c>
+      <c r="P37">
+        <v>27.2398390685795</v>
+      </c>
+      <c r="Q37">
+        <v>43.7398390685795</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1139291755512706</v>
+      </c>
+      <c r="T37">
+        <v>1.053499844544208</v>
+      </c>
+      <c r="U37">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V37">
+        <v>0.15</v>
+      </c>
+      <c r="W37">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>2.229303351071141</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1015570544026135</v>
+      </c>
+      <c r="C38">
+        <v>411.1462127186296</v>
+      </c>
+      <c r="D38">
+        <v>641.9156088649024</v>
+      </c>
+      <c r="E38">
+        <v>197.8544068510705</v>
+      </c>
+      <c r="F38">
+        <v>293.3693961462728</v>
+      </c>
+      <c r="G38">
+        <v>62.6</v>
+      </c>
+      <c r="H38">
+        <v>719.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>74.616</v>
+      </c>
+      <c r="K38">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L38">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M38">
+        <v>26.81396280776934</v>
+      </c>
+      <c r="N38">
+        <v>31.30203719223067</v>
+      </c>
+      <c r="O38">
+        <v>4.695305578834601</v>
+      </c>
+      <c r="P38">
+        <v>26.60673161339606</v>
+      </c>
+      <c r="Q38">
+        <v>43.10673161339606</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1149822725040836</v>
+      </c>
+      <c r="T38">
+        <v>1.068266910307113</v>
+      </c>
+      <c r="U38">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V38">
+        <v>0.15</v>
+      </c>
+      <c r="W38">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>2.167378257985832</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1018686446969011</v>
+      </c>
+      <c r="C39">
+        <v>400.0616565221425</v>
+      </c>
+      <c r="D39">
+        <v>638.9802025613674</v>
+      </c>
+      <c r="E39">
+        <v>206.0035567440225</v>
+      </c>
+      <c r="F39">
+        <v>301.5185460392249</v>
+      </c>
+      <c r="G39">
+        <v>62.6</v>
+      </c>
+      <c r="H39">
+        <v>719.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>74.616</v>
+      </c>
+      <c r="K39">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L39">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M39">
+        <v>27.55879510798515</v>
+      </c>
+      <c r="N39">
+        <v>30.55720489201485</v>
+      </c>
+      <c r="O39">
+        <v>4.583580733802228</v>
+      </c>
+      <c r="P39">
+        <v>25.97362415821262</v>
+      </c>
+      <c r="Q39">
+        <v>42.47362415821262</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1160688011061922</v>
+      </c>
+      <c r="T39">
+        <v>1.083502771808524</v>
+      </c>
+      <c r="U39">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V39">
+        <v>0.15</v>
+      </c>
+      <c r="W39">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>2.108800467229458</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1021802349911887</v>
+      </c>
+      <c r="C40">
+        <v>389.0038246696176</v>
+      </c>
+      <c r="D40">
+        <v>636.0715206017944</v>
+      </c>
+      <c r="E40">
+        <v>214.1527066369745</v>
+      </c>
+      <c r="F40">
+        <v>309.6676959321769</v>
+      </c>
+      <c r="G40">
+        <v>62.6</v>
+      </c>
+      <c r="H40">
+        <v>719.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>74.616</v>
+      </c>
+      <c r="K40">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L40">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M40">
+        <v>28.30362740820097</v>
+      </c>
+      <c r="N40">
+        <v>29.81237259179904</v>
+      </c>
+      <c r="O40">
+        <v>4.471855888769857</v>
+      </c>
+      <c r="P40">
+        <v>25.34051670302918</v>
+      </c>
+      <c r="Q40">
+        <v>41.84051670302918</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1171903790180463</v>
+      </c>
+      <c r="T40">
+        <v>1.099230112713205</v>
+      </c>
+      <c r="U40">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V40">
+        <v>0.15</v>
+      </c>
+      <c r="W40">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>2.053305718091841</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1024918252854763</v>
+      </c>
+      <c r="C41">
+        <v>377.9723538616472</v>
+      </c>
+      <c r="D41">
+        <v>633.1891996867761</v>
+      </c>
+      <c r="E41">
+        <v>222.3018565299266</v>
+      </c>
+      <c r="F41">
+        <v>317.8168458251289</v>
+      </c>
+      <c r="G41">
+        <v>62.6</v>
+      </c>
+      <c r="H41">
+        <v>719.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>74.616</v>
+      </c>
+      <c r="K41">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L41">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M41">
+        <v>29.04845970841678</v>
+      </c>
+      <c r="N41">
+        <v>29.06754029158322</v>
+      </c>
+      <c r="O41">
+        <v>4.360131043737485</v>
+      </c>
+      <c r="P41">
+        <v>24.70740924784574</v>
+      </c>
+      <c r="Q41">
+        <v>41.20740924784573</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1183487299761907</v>
+      </c>
+      <c r="T41">
+        <v>1.115473104139352</v>
+      </c>
+      <c r="U41">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V41">
+        <v>0.15</v>
+      </c>
+      <c r="W41">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>2.000656853525384</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1099774155797639</v>
+      </c>
+      <c r="C42">
+        <v>307.6598704682073</v>
+      </c>
+      <c r="D42">
+        <v>571.0258661862882</v>
+      </c>
+      <c r="E42">
+        <v>230.4510064228786</v>
+      </c>
+      <c r="F42">
+        <v>325.9659957180809</v>
+      </c>
+      <c r="G42">
+        <v>62.6</v>
+      </c>
+      <c r="H42">
+        <v>719.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>74.616</v>
+      </c>
+      <c r="K42">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L42">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M42">
+        <v>36.6711745182841</v>
+      </c>
+      <c r="N42">
+        <v>21.4448254817159</v>
+      </c>
+      <c r="O42">
+        <v>3.216723822257386</v>
+      </c>
+      <c r="P42">
+        <v>18.22810165945852</v>
+      </c>
+      <c r="Q42">
+        <v>34.72810165945851</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1195456926329399</v>
+      </c>
+      <c r="T42">
+        <v>1.132257528613036</v>
+      </c>
+      <c r="U42">
+        <v>0.1125</v>
+      </c>
+      <c r="V42">
+        <v>0.15</v>
+      </c>
+      <c r="W42">
+        <v>0.095625</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>1.584786982239241</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1104683558740515</v>
+      </c>
+      <c r="C43">
+        <v>295.8575340941816</v>
+      </c>
+      <c r="D43">
+        <v>567.3726797052145</v>
+      </c>
+      <c r="E43">
+        <v>238.6001563158306</v>
+      </c>
+      <c r="F43">
+        <v>334.115145611033</v>
+      </c>
+      <c r="G43">
+        <v>62.6</v>
+      </c>
+      <c r="H43">
+        <v>719.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>74.616</v>
+      </c>
+      <c r="K43">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L43">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M43">
+        <v>37.58795388124121</v>
+      </c>
+      <c r="N43">
+        <v>20.52804611875879</v>
+      </c>
+      <c r="O43">
+        <v>3.07920691781382</v>
+      </c>
+      <c r="P43">
+        <v>17.44883920094497</v>
+      </c>
+      <c r="Q43">
+        <v>33.94883920094497</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1207832302950026</v>
+      </c>
+      <c r="T43">
+        <v>1.149610916628202</v>
+      </c>
+      <c r="U43">
+        <v>0.1125</v>
+      </c>
+      <c r="V43">
+        <v>0.15</v>
+      </c>
+      <c r="W43">
+        <v>0.095625</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>1.546133641209015</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1109592961683392</v>
+      </c>
+      <c r="C44">
+        <v>284.1016437195482</v>
+      </c>
+      <c r="D44">
+        <v>563.7659392235331</v>
+      </c>
+      <c r="E44">
+        <v>246.7493062087826</v>
+      </c>
+      <c r="F44">
+        <v>342.264295503985</v>
+      </c>
+      <c r="G44">
+        <v>62.6</v>
+      </c>
+      <c r="H44">
+        <v>719.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>74.616</v>
+      </c>
+      <c r="K44">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L44">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M44">
+        <v>38.50473324419831</v>
+      </c>
+      <c r="N44">
+        <v>19.6112667558017</v>
+      </c>
+      <c r="O44">
+        <v>2.941690013370255</v>
+      </c>
+      <c r="P44">
+        <v>16.66957674243145</v>
+      </c>
+      <c r="Q44">
+        <v>33.16957674243144</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1220634416695503</v>
+      </c>
+      <c r="T44">
+        <v>1.167562697333545</v>
+      </c>
+      <c r="U44">
+        <v>0.1125</v>
+      </c>
+      <c r="V44">
+        <v>0.15</v>
+      </c>
+      <c r="W44">
+        <v>0.095625</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>1.509320935465944</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1446921306991933</v>
+      </c>
+      <c r="C45">
+        <v>104.5659212168409</v>
+      </c>
+      <c r="D45">
+        <v>392.3793666137779</v>
+      </c>
+      <c r="E45">
+        <v>254.8984561017347</v>
+      </c>
+      <c r="F45">
+        <v>350.413445396937</v>
+      </c>
+      <c r="G45">
+        <v>62.6</v>
+      </c>
+      <c r="H45">
+        <v>719.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>74.616</v>
+      </c>
+      <c r="K45">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L45">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M45">
+        <v>68.89128336503781</v>
+      </c>
+      <c r="N45">
+        <v>-10.7752833650378</v>
+      </c>
+      <c r="O45">
+        <v>-1.61629250475567</v>
+      </c>
+      <c r="P45">
+        <v>-9.158990860282131</v>
+      </c>
+      <c r="Q45">
+        <v>7.341009139717862</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1243007768935231</v>
+      </c>
+      <c r="T45">
+        <v>1.198935759707165</v>
+      </c>
+      <c r="U45">
+        <v>0.1966</v>
+      </c>
+      <c r="V45">
+        <v>0.1265385049340519</v>
+      </c>
+      <c r="W45">
+        <v>0.1717225299299654</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.8435900328936791</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1462701306991933</v>
+      </c>
+      <c r="C46">
+        <v>90.91496043764477</v>
+      </c>
+      <c r="D46">
+        <v>386.8775557275338</v>
+      </c>
+      <c r="E46">
+        <v>263.0476059946867</v>
+      </c>
+      <c r="F46">
+        <v>358.562595289889</v>
+      </c>
+      <c r="G46">
+        <v>62.6</v>
+      </c>
+      <c r="H46">
+        <v>719.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>74.616</v>
+      </c>
+      <c r="K46">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L46">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M46">
+        <v>70.49340623399219</v>
+      </c>
+      <c r="N46">
+        <v>-12.37740623399218</v>
+      </c>
+      <c r="O46">
+        <v>-1.856610935098828</v>
+      </c>
+      <c r="P46">
+        <v>-10.52079529889335</v>
+      </c>
+      <c r="Q46">
+        <v>5.979204701106639</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1258275764809074</v>
+      </c>
+      <c r="T46">
+        <v>1.220345326844793</v>
+      </c>
+      <c r="U46">
+        <v>0.1966</v>
+      </c>
+      <c r="V46">
+        <v>0.1236626298219143</v>
+      </c>
+      <c r="W46">
+        <v>0.1722879269770116</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.8244175321460953</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1478481306991933</v>
+      </c>
+      <c r="C47">
+        <v>77.41615525031739</v>
+      </c>
+      <c r="D47">
+        <v>381.5279004331584</v>
+      </c>
+      <c r="E47">
+        <v>271.1967558876387</v>
+      </c>
+      <c r="F47">
+        <v>366.7117451828411</v>
+      </c>
+      <c r="G47">
+        <v>62.6</v>
+      </c>
+      <c r="H47">
+        <v>719.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>74.616</v>
+      </c>
+      <c r="K47">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L47">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M47">
+        <v>72.09552910294656</v>
+      </c>
+      <c r="N47">
+        <v>-13.97952910294655</v>
+      </c>
+      <c r="O47">
+        <v>-2.096929365441983</v>
+      </c>
+      <c r="P47">
+        <v>-11.88259973750457</v>
+      </c>
+      <c r="Q47">
+        <v>4.617400262495426</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1274098960532876</v>
+      </c>
+      <c r="T47">
+        <v>1.242533423696517</v>
+      </c>
+      <c r="U47">
+        <v>0.1966</v>
+      </c>
+      <c r="V47">
+        <v>0.1209145713814273</v>
+      </c>
+      <c r="W47">
+        <v>0.1728281952664114</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.8060971425428487</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1575637387854326</v>
+      </c>
+      <c r="C48">
+        <v>39.33352426670086</v>
+      </c>
+      <c r="D48">
+        <v>351.5944193424939</v>
+      </c>
+      <c r="E48">
+        <v>279.3459057805907</v>
+      </c>
+      <c r="F48">
+        <v>374.8608950757931</v>
+      </c>
+      <c r="G48">
+        <v>62.6</v>
+      </c>
+      <c r="H48">
+        <v>719.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>74.616</v>
+      </c>
+      <c r="K48">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L48">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M48">
+        <v>80.14525936720455</v>
+      </c>
+      <c r="N48">
+        <v>-22.02925936720454</v>
+      </c>
+      <c r="O48">
+        <v>-3.304388905080681</v>
+      </c>
+      <c r="P48">
+        <v>-18.72487046212386</v>
+      </c>
+      <c r="Q48">
+        <v>-2.224870462123864</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1294686128065693</v>
+      </c>
+      <c r="T48">
+        <v>1.271401806234041</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.1087700017297238</v>
+      </c>
+      <c r="W48">
+        <v>0.190544973630185</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.7251333448648254</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1593137387854326</v>
+      </c>
+      <c r="C49">
+        <v>26.2849333385289</v>
+      </c>
+      <c r="D49">
+        <v>346.694978307274</v>
+      </c>
+      <c r="E49">
+        <v>287.4950556735428</v>
+      </c>
+      <c r="F49">
+        <v>383.0100449687451</v>
+      </c>
+      <c r="G49">
+        <v>62.6</v>
+      </c>
+      <c r="H49">
+        <v>719.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>74.616</v>
+      </c>
+      <c r="K49">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L49">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M49">
+        <v>81.8875476143177</v>
+      </c>
+      <c r="N49">
+        <v>-23.77154761431769</v>
+      </c>
+      <c r="O49">
+        <v>-3.565732142147654</v>
+      </c>
+      <c r="P49">
+        <v>-20.20581547217004</v>
+      </c>
+      <c r="Q49">
+        <v>-3.705815472170045</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1311793413500895</v>
+      </c>
+      <c r="T49">
+        <v>1.295390519559212</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.1064557463737722</v>
+      </c>
+      <c r="W49">
+        <v>0.1910397614252875</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.7097049758251481</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1610637387854326</v>
+      </c>
+      <c r="C50">
+        <v>13.37101245730923</v>
+      </c>
+      <c r="D50">
+        <v>341.9302073190063</v>
+      </c>
+      <c r="E50">
+        <v>295.6442055664947</v>
+      </c>
+      <c r="F50">
+        <v>391.1591948616971</v>
+      </c>
+      <c r="G50">
+        <v>62.6</v>
+      </c>
+      <c r="H50">
+        <v>719.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>74.616</v>
+      </c>
+      <c r="K50">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L50">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M50">
+        <v>83.62983586143083</v>
+      </c>
+      <c r="N50">
+        <v>-25.51383586143083</v>
+      </c>
+      <c r="O50">
+        <v>-3.827075379214625</v>
+      </c>
+      <c r="P50">
+        <v>-21.6867604822162</v>
+      </c>
+      <c r="Q50">
+        <v>-5.186760482216208</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1329558671452836</v>
+      </c>
+      <c r="T50">
+        <v>1.320301875704581</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.1042379183243186</v>
+      </c>
+      <c r="W50">
+        <v>0.1915139330622607</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.6949194554954576</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1628137387854326</v>
+      </c>
+      <c r="C51">
+        <v>0.5862844217346606</v>
+      </c>
+      <c r="D51">
+        <v>337.2946291763838</v>
+      </c>
+      <c r="E51">
+        <v>303.7933554594468</v>
+      </c>
+      <c r="F51">
+        <v>399.3083447546491</v>
+      </c>
+      <c r="G51">
+        <v>62.6</v>
+      </c>
+      <c r="H51">
+        <v>719.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>74.616</v>
+      </c>
+      <c r="K51">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L51">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M51">
+        <v>85.37212410854397</v>
+      </c>
+      <c r="N51">
+        <v>-27.25612410854396</v>
+      </c>
+      <c r="O51">
+        <v>-4.088418616281595</v>
+      </c>
+      <c r="P51">
+        <v>-23.16770549226237</v>
+      </c>
+      <c r="Q51">
+        <v>-6.667705492262378</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1348020606187205</v>
+      </c>
+      <c r="T51">
+        <v>1.34619014777722</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0.1021106138687203</v>
+      </c>
+      <c r="W51">
+        <v>0.1919687507548676</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.6807374257914687</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1645637387854326</v>
+      </c>
+      <c r="C52">
+        <v>-12.07443492274666</v>
+      </c>
+      <c r="D52">
+        <v>332.7830597248545</v>
+      </c>
+      <c r="E52">
+        <v>311.9425053523988</v>
+      </c>
+      <c r="F52">
+        <v>407.4574946476012</v>
+      </c>
+      <c r="G52">
+        <v>62.6</v>
+      </c>
+      <c r="H52">
+        <v>719.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>74.616</v>
+      </c>
+      <c r="K52">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L52">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M52">
+        <v>87.11441235565712</v>
+      </c>
+      <c r="N52">
+        <v>-28.99841235565712</v>
+      </c>
+      <c r="O52">
+        <v>-4.349761853348568</v>
+      </c>
+      <c r="P52">
+        <v>-24.64865050230855</v>
+      </c>
+      <c r="Q52">
+        <v>-8.148650502308556</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1367221018310949</v>
+      </c>
+      <c r="T52">
+        <v>1.373113950732765</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.1000684015913459</v>
+      </c>
+      <c r="W52">
+        <v>0.1924053757397702</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.6671226772756392</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1663137387854326</v>
+      </c>
+      <c r="C53">
+        <v>-24.61605602385129</v>
+      </c>
+      <c r="D53">
+        <v>328.3905885167019</v>
+      </c>
+      <c r="E53">
+        <v>320.0916552453509</v>
+      </c>
+      <c r="F53">
+        <v>415.6066445405532</v>
+      </c>
+      <c r="G53">
+        <v>62.6</v>
+      </c>
+      <c r="H53">
+        <v>719.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>74.616</v>
+      </c>
+      <c r="K53">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L53">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M53">
+        <v>88.85670060277027</v>
+      </c>
+      <c r="N53">
+        <v>-30.74070060277027</v>
+      </c>
+      <c r="O53">
+        <v>-4.611105090415541</v>
+      </c>
+      <c r="P53">
+        <v>-26.12959551235473</v>
+      </c>
+      <c r="Q53">
+        <v>-9.629595512354733</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1387205120725458</v>
+      </c>
+      <c r="T53">
+        <v>1.401136684421189</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.09810627606994694</v>
+      </c>
+      <c r="W53">
+        <v>0.1928248781762453</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.6540418404663129</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1680637387854326</v>
+      </c>
+      <c r="C54">
+        <v>-37.04323345070054</v>
+      </c>
+      <c r="D54">
+        <v>324.1125609828047</v>
+      </c>
+      <c r="E54">
+        <v>328.2408051383029</v>
+      </c>
+      <c r="F54">
+        <v>423.7557944335052</v>
+      </c>
+      <c r="G54">
+        <v>62.6</v>
+      </c>
+      <c r="H54">
+        <v>719.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>74.616</v>
+      </c>
+      <c r="K54">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L54">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M54">
+        <v>90.59898884988341</v>
+      </c>
+      <c r="N54">
+        <v>-32.48298884988341</v>
+      </c>
+      <c r="O54">
+        <v>-4.872448327482512</v>
+      </c>
+      <c r="P54">
+        <v>-27.61054052240089</v>
+      </c>
+      <c r="Q54">
+        <v>-11.1105405224009</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1408021894073905</v>
+      </c>
+      <c r="T54">
+        <v>1.430327032013297</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.09621961691475567</v>
+      </c>
+      <c r="W54">
+        <v>0.1932282459036252</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.6414641127650378</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1698137387854326</v>
+      </c>
+      <c r="C55">
+        <v>-49.36038234646662</v>
+      </c>
+      <c r="D55">
+        <v>319.9445619799906</v>
+      </c>
+      <c r="E55">
+        <v>336.3899550312549</v>
+      </c>
+      <c r="F55">
+        <v>431.9049443264573</v>
+      </c>
+      <c r="G55">
+        <v>62.6</v>
+      </c>
+      <c r="H55">
+        <v>719.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>74.616</v>
+      </c>
+      <c r="K55">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L55">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M55">
+        <v>92.34127709699656</v>
+      </c>
+      <c r="N55">
+        <v>-34.22527709699656</v>
+      </c>
+      <c r="O55">
+        <v>-5.133791564549484</v>
+      </c>
+      <c r="P55">
+        <v>-29.09148553244707</v>
+      </c>
+      <c r="Q55">
+        <v>-12.59148553244708</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.142972448756484</v>
+      </c>
+      <c r="T55">
+        <v>1.460759522056133</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.09440415244466592</v>
+      </c>
+      <c r="W55">
+        <v>0.1936163922073304</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.6293610162977727</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1715637387854326</v>
+      </c>
+      <c r="C56">
+        <v>-61.57169362767377</v>
+      </c>
+      <c r="D56">
+        <v>315.8824005917355</v>
+      </c>
+      <c r="E56">
+        <v>344.5391049242069</v>
+      </c>
+      <c r="F56">
+        <v>440.0540942194093</v>
+      </c>
+      <c r="G56">
+        <v>62.6</v>
+      </c>
+      <c r="H56">
+        <v>719.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>74.616</v>
+      </c>
+      <c r="K56">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L56">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M56">
+        <v>94.08356534410969</v>
+      </c>
+      <c r="N56">
+        <v>-35.96756534410968</v>
+      </c>
+      <c r="O56">
+        <v>-5.395134801616453</v>
+      </c>
+      <c r="P56">
+        <v>-30.57243054249323</v>
+      </c>
+      <c r="Q56">
+        <v>-14.07243054249323</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1452370672077119</v>
+      </c>
+      <c r="T56">
+        <v>1.492515163839962</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.09265592739939436</v>
+      </c>
+      <c r="W56">
+        <v>0.1939901627220095</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.6177061826626289</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1733137387854326</v>
+      </c>
+      <c r="C57">
+        <v>-73.68114804015505</v>
+      </c>
+      <c r="D57">
+        <v>311.9220960722062</v>
+      </c>
+      <c r="E57">
+        <v>352.688254817159</v>
+      </c>
+      <c r="F57">
+        <v>448.2032441123613</v>
+      </c>
+      <c r="G57">
+        <v>62.6</v>
+      </c>
+      <c r="H57">
+        <v>719.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>74.616</v>
+      </c>
+      <c r="K57">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L57">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M57">
+        <v>95.82585359122284</v>
+      </c>
+      <c r="N57">
+        <v>-37.70985359122283</v>
+      </c>
+      <c r="O57">
+        <v>-5.656478038683425</v>
+      </c>
+      <c r="P57">
+        <v>-32.05337555253941</v>
+      </c>
+      <c r="Q57">
+        <v>-15.55337555253941</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1476023353678833</v>
+      </c>
+      <c r="T57">
+        <v>1.52568216748085</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.09097127417395082</v>
+      </c>
+      <c r="W57">
+        <v>0.1943503415816093</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.606475161159672</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1750637387854326</v>
+      </c>
+      <c r="C58">
+        <v>-85.6925291707588</v>
+      </c>
+      <c r="D58">
+        <v>308.0598648345545</v>
+      </c>
+      <c r="E58">
+        <v>360.837404710111</v>
+      </c>
+      <c r="F58">
+        <v>456.3523940053133</v>
+      </c>
+      <c r="G58">
+        <v>62.6</v>
+      </c>
+      <c r="H58">
+        <v>719.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>74.616</v>
+      </c>
+      <c r="K58">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L58">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M58">
+        <v>97.56814183833599</v>
+      </c>
+      <c r="N58">
+        <v>-39.45214183833598</v>
+      </c>
+      <c r="O58">
+        <v>-5.917821275750399</v>
+      </c>
+      <c r="P58">
+        <v>-33.53432056258558</v>
+      </c>
+      <c r="Q58">
+        <v>-17.03432056258559</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1500751157171533</v>
+      </c>
+      <c r="T58">
+        <v>1.560356762196324</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.08934678713513027</v>
+      </c>
+      <c r="W58">
+        <v>0.1946976569105091</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.5956452475675349</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1768137387854326</v>
+      </c>
+      <c r="C59">
+        <v>-97.60943550421126</v>
+      </c>
+      <c r="D59">
+        <v>304.2921083940541</v>
+      </c>
+      <c r="E59">
+        <v>368.986554603063</v>
+      </c>
+      <c r="F59">
+        <v>464.5015438982654</v>
+      </c>
+      <c r="G59">
+        <v>62.6</v>
+      </c>
+      <c r="H59">
+        <v>719.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>74.616</v>
+      </c>
+      <c r="K59">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L59">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M59">
+        <v>99.31043008544913</v>
+      </c>
+      <c r="N59">
+        <v>-41.19443008544912</v>
+      </c>
+      <c r="O59">
+        <v>-6.179164512817369</v>
+      </c>
+      <c r="P59">
+        <v>-35.01526557263175</v>
+      </c>
+      <c r="Q59">
+        <v>-18.51526557263175</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1526629091059243</v>
+      </c>
+      <c r="T59">
+        <v>1.596644128759029</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.08777929964153149</v>
+      </c>
+      <c r="W59">
+        <v>0.1950327857366405</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.5851953309435431</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1785637387854326</v>
+      </c>
+      <c r="C60">
+        <v>-109.435291605892</v>
+      </c>
+      <c r="D60">
+        <v>300.6154021853253</v>
+      </c>
+      <c r="E60">
+        <v>377.135704496015</v>
+      </c>
+      <c r="F60">
+        <v>472.6506937912173</v>
+      </c>
+      <c r="G60">
+        <v>62.6</v>
+      </c>
+      <c r="H60">
+        <v>719.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>74.616</v>
+      </c>
+      <c r="K60">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L60">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M60">
+        <v>101.0527183325623</v>
+      </c>
+      <c r="N60">
+        <v>-42.93671833256224</v>
+      </c>
+      <c r="O60">
+        <v>-6.440507749884337</v>
+      </c>
+      <c r="P60">
+        <v>-36.4962105826779</v>
+      </c>
+      <c r="Q60">
+        <v>-19.99621058267791</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1553739307513035</v>
+      </c>
+      <c r="T60">
+        <v>1.634659465158053</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.08626586344081545</v>
+      </c>
+      <c r="W60">
+        <v>0.1953563583963537</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.5751057562721029</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1803137387854326</v>
+      </c>
+      <c r="C61">
+        <v>-121.1733585035735</v>
+      </c>
+      <c r="D61">
+        <v>297.0264851805958</v>
+      </c>
+      <c r="E61">
+        <v>385.284854388967</v>
+      </c>
+      <c r="F61">
+        <v>480.7998436841693</v>
+      </c>
+      <c r="G61">
+        <v>62.6</v>
+      </c>
+      <c r="H61">
+        <v>719.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>74.616</v>
+      </c>
+      <c r="K61">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L61">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M61">
+        <v>102.7950065796754</v>
+      </c>
+      <c r="N61">
+        <v>-44.6790065796754</v>
+      </c>
+      <c r="O61">
+        <v>-6.70185098695131</v>
+      </c>
+      <c r="P61">
+        <v>-37.97715559272409</v>
+      </c>
+      <c r="Q61">
+        <v>-21.4771555927241</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1582171973549938</v>
+      </c>
+      <c r="T61">
+        <v>1.674529208210688</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.08480373016215755</v>
+      </c>
+      <c r="W61">
+        <v>0.1956689624913307</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.5653582010810503</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1820637387854326</v>
+      </c>
+      <c r="C62">
+        <v>-132.8267433342736</v>
+      </c>
+      <c r="D62">
+        <v>293.5222502428477</v>
+      </c>
+      <c r="E62">
+        <v>393.434004281919</v>
+      </c>
+      <c r="F62">
+        <v>488.9489935771214</v>
+      </c>
+      <c r="G62">
+        <v>62.6</v>
+      </c>
+      <c r="H62">
+        <v>719.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>74.616</v>
+      </c>
+      <c r="K62">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L62">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M62">
+        <v>104.5372948267885</v>
+      </c>
+      <c r="N62">
+        <v>-46.42129482678853</v>
+      </c>
+      <c r="O62">
+        <v>-6.963194224018281</v>
+      </c>
+      <c r="P62">
+        <v>-39.45810060277025</v>
+      </c>
+      <c r="Q62">
+        <v>-22.95810060277026</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1612026272888686</v>
+      </c>
+      <c r="T62">
+        <v>1.716392438415956</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.08339033465945492</v>
+      </c>
+      <c r="W62">
+        <v>0.1959711464498085</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5559355643963662</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1838137387854326</v>
+      </c>
+      <c r="C63">
+        <v>-144.3984083162069</v>
+      </c>
+      <c r="D63">
+        <v>290.0997351538665</v>
+      </c>
+      <c r="E63">
+        <v>401.5831541748711</v>
+      </c>
+      <c r="F63">
+        <v>497.0981434700734</v>
+      </c>
+      <c r="G63">
+        <v>62.6</v>
+      </c>
+      <c r="H63">
+        <v>719.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>74.616</v>
+      </c>
+      <c r="K63">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L63">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M63">
+        <v>106.2795830739017</v>
+      </c>
+      <c r="N63">
+        <v>-48.16358307390168</v>
+      </c>
+      <c r="O63">
+        <v>-7.224537461085253</v>
+      </c>
+      <c r="P63">
+        <v>-40.93904561281643</v>
+      </c>
+      <c r="Q63">
+        <v>-24.43904561281644</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1643411561937115</v>
+      </c>
+      <c r="T63">
+        <v>1.760402500939442</v>
+      </c>
+      <c r="U63">
+        <v>0.2138</v>
+      </c>
+      <c r="V63">
+        <v>0.08202327999290647</v>
+      </c>
+      <c r="W63">
+        <v>0.1962634227375166</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.5468218666193765</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1855637387854326</v>
+      </c>
+      <c r="C64">
+        <v>-155.8911791002834</v>
+      </c>
+      <c r="D64">
+        <v>286.756114262742</v>
+      </c>
+      <c r="E64">
+        <v>409.7323040678231</v>
+      </c>
+      <c r="F64">
+        <v>505.2472933630254</v>
+      </c>
+      <c r="G64">
+        <v>62.6</v>
+      </c>
+      <c r="H64">
+        <v>719.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>74.616</v>
+      </c>
+      <c r="K64">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L64">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M64">
+        <v>108.0218713210148</v>
+      </c>
+      <c r="N64">
+        <v>-49.90587132101484</v>
+      </c>
+      <c r="O64">
+        <v>-7.485880698152227</v>
+      </c>
+      <c r="P64">
+        <v>-42.41999062286261</v>
+      </c>
+      <c r="Q64">
+        <v>-25.91999062286261</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.167644870830388</v>
+      </c>
+      <c r="T64">
+        <v>1.806728882543112</v>
+      </c>
+      <c r="U64">
+        <v>0.2138</v>
+      </c>
+      <c r="V64">
+        <v>0.08070032386398862</v>
+      </c>
+      <c r="W64">
+        <v>0.1965462707578792</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.5380021590932573</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1873137387854326</v>
+      </c>
+      <c r="C65">
+        <v>-167.3077525506445</v>
+      </c>
+      <c r="D65">
+        <v>283.4886907053329</v>
+      </c>
+      <c r="E65">
+        <v>417.8814539607752</v>
+      </c>
+      <c r="F65">
+        <v>513.3964432559775</v>
+      </c>
+      <c r="G65">
+        <v>62.6</v>
+      </c>
+      <c r="H65">
+        <v>719.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>74.616</v>
+      </c>
+      <c r="K65">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L65">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M65">
+        <v>109.764159568128</v>
+      </c>
+      <c r="N65">
+        <v>-51.64815956812797</v>
+      </c>
+      <c r="O65">
+        <v>-7.747223935219197</v>
+      </c>
+      <c r="P65">
+        <v>-43.90093563290878</v>
+      </c>
+      <c r="Q65">
+        <v>-27.40093563290878</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1711271646366148</v>
+      </c>
+      <c r="T65">
+        <v>1.855559392882115</v>
+      </c>
+      <c r="U65">
+        <v>0.2138</v>
+      </c>
+      <c r="V65">
+        <v>0.07941936634233801</v>
+      </c>
+      <c r="W65">
+        <v>0.1968201394760081</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.5294624422822534</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1890637387854326</v>
+      </c>
+      <c r="C66">
+        <v>-178.6507039992622</v>
+      </c>
+      <c r="D66">
+        <v>280.2948891496673</v>
+      </c>
+      <c r="E66">
+        <v>426.0306038537271</v>
+      </c>
+      <c r="F66">
+        <v>521.5455931489295</v>
+      </c>
+      <c r="G66">
+        <v>62.6</v>
+      </c>
+      <c r="H66">
+        <v>719.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>74.616</v>
+      </c>
+      <c r="K66">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L66">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M66">
+        <v>111.5064478152411</v>
+      </c>
+      <c r="N66">
+        <v>-53.39044781524111</v>
+      </c>
+      <c r="O66">
+        <v>-8.008567172286167</v>
+      </c>
+      <c r="P66">
+        <v>-45.38188064295494</v>
+      </c>
+      <c r="Q66">
+        <v>-28.88188064295495</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1748029192098541</v>
+      </c>
+      <c r="T66">
+        <v>1.907102709351063</v>
+      </c>
+      <c r="U66">
+        <v>0.2138</v>
+      </c>
+      <c r="V66">
+        <v>0.07817843874323899</v>
+      </c>
+      <c r="W66">
+        <v>0.1970854497966955</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.5211895916215932</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1908137387854326</v>
+      </c>
+      <c r="C67">
+        <v>-189.9224940156172</v>
+      </c>
+      <c r="D67">
+        <v>277.1722490262643</v>
+      </c>
+      <c r="E67">
+        <v>434.1797537466792</v>
+      </c>
+      <c r="F67">
+        <v>529.6947430418816</v>
+      </c>
+      <c r="G67">
+        <v>62.6</v>
+      </c>
+      <c r="H67">
+        <v>719.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>74.616</v>
+      </c>
+      <c r="K67">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L67">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M67">
+        <v>113.2487360623543</v>
+      </c>
+      <c r="N67">
+        <v>-55.13273606235426</v>
+      </c>
+      <c r="O67">
+        <v>-8.269910409353141</v>
+      </c>
+      <c r="P67">
+        <v>-46.86282565300112</v>
+      </c>
+      <c r="Q67">
+        <v>-30.36282565300113</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1786887169015642</v>
+      </c>
+      <c r="T67">
+        <v>1.961591358189664</v>
+      </c>
+      <c r="U67">
+        <v>0.2138</v>
+      </c>
+      <c r="V67">
+        <v>0.07697569353180453</v>
+      </c>
+      <c r="W67">
+        <v>0.1973425967229002</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.5131712902120302</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1925637387854326</v>
+      </c>
+      <c r="C68">
+        <v>-201.1254747288546</v>
+      </c>
+      <c r="D68">
+        <v>274.1184182059789</v>
+      </c>
+      <c r="E68">
+        <v>442.3289036396312</v>
+      </c>
+      <c r="F68">
+        <v>537.8438929348335</v>
+      </c>
+      <c r="G68">
+        <v>62.6</v>
+      </c>
+      <c r="H68">
+        <v>719.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>74.616</v>
+      </c>
+      <c r="K68">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L68">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M68">
+        <v>114.9910243094674</v>
+      </c>
+      <c r="N68">
+        <v>-56.8750243094674</v>
+      </c>
+      <c r="O68">
+        <v>-8.531253646420112</v>
+      </c>
+      <c r="P68">
+        <v>-48.34377066304729</v>
+      </c>
+      <c r="Q68">
+        <v>-31.84377066304729</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1828030909280808</v>
+      </c>
+      <c r="T68">
+        <v>2.019285221665831</v>
+      </c>
+      <c r="U68">
+        <v>0.2138</v>
+      </c>
+      <c r="V68">
+        <v>0.07580939514495902</v>
+      </c>
+      <c r="W68">
+        <v>0.1975919513180077</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.5053959676330599</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.211333708728137</v>
+      </c>
+      <c r="C69">
+        <v>-238.2447055555025</v>
+      </c>
+      <c r="D69">
+        <v>245.148337272283</v>
+      </c>
+      <c r="E69">
+        <v>450.4780535325832</v>
+      </c>
+      <c r="F69">
+        <v>545.9930428277855</v>
+      </c>
+      <c r="G69">
+        <v>62.6</v>
+      </c>
+      <c r="H69">
+        <v>719.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>74.616</v>
+      </c>
+      <c r="K69">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L69">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M69">
+        <v>130.3831386272752</v>
+      </c>
+      <c r="N69">
+        <v>-72.26713862727519</v>
+      </c>
+      <c r="O69">
+        <v>-10.84007079409128</v>
+      </c>
+      <c r="P69">
+        <v>-61.42706783318391</v>
+      </c>
+      <c r="Q69">
+        <v>-44.92706783318391</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1879849116916722</v>
+      </c>
+      <c r="T69">
+        <v>2.091947370941968</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.06685987231002573</v>
+      </c>
+      <c r="W69">
+        <v>0.2228338624923659</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.4457324820668381</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.213333708728137</v>
+      </c>
+      <c r="C70">
+        <v>-249.1237356738877</v>
+      </c>
+      <c r="D70">
+        <v>242.4184570468499</v>
+      </c>
+      <c r="E70">
+        <v>458.6272034255353</v>
+      </c>
+      <c r="F70">
+        <v>554.1421927207376</v>
+      </c>
+      <c r="G70">
+        <v>62.6</v>
+      </c>
+      <c r="H70">
+        <v>719.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>74.616</v>
+      </c>
+      <c r="K70">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L70">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M70">
+        <v>132.3291556217121</v>
+      </c>
+      <c r="N70">
+        <v>-74.21315562171213</v>
+      </c>
+      <c r="O70">
+        <v>-11.13197334325682</v>
+      </c>
+      <c r="P70">
+        <v>-63.08118227845531</v>
+      </c>
+      <c r="Q70">
+        <v>-46.58118227845532</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.192646940182037</v>
+      </c>
+      <c r="T70">
+        <v>2.157320726283904</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.06587663889370182</v>
+      </c>
+      <c r="W70">
+        <v>0.223068658632184</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.4391775926246787</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.215333708728137</v>
+      </c>
+      <c r="C71">
+        <v>-259.9426375073396</v>
+      </c>
+      <c r="D71">
+        <v>239.74870510635</v>
+      </c>
+      <c r="E71">
+        <v>466.7763533184873</v>
+      </c>
+      <c r="F71">
+        <v>562.2913426136896</v>
+      </c>
+      <c r="G71">
+        <v>62.6</v>
+      </c>
+      <c r="H71">
+        <v>719.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>74.616</v>
+      </c>
+      <c r="K71">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L71">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M71">
+        <v>134.2751726161491</v>
+      </c>
+      <c r="N71">
+        <v>-76.15917261614908</v>
+      </c>
+      <c r="O71">
+        <v>-11.42387589242236</v>
+      </c>
+      <c r="P71">
+        <v>-64.73529672372672</v>
+      </c>
+      <c r="Q71">
+        <v>-48.23529672372673</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1976097447040381</v>
+      </c>
+      <c r="T71">
+        <v>2.226911717454353</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.06492190499669163</v>
+      </c>
+      <c r="W71">
+        <v>0.2232966490867901</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.4328126999779442</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.217333708728137</v>
+      </c>
+      <c r="C72">
+        <v>-270.7033759925566</v>
+      </c>
+      <c r="D72">
+        <v>237.1371165140851</v>
+      </c>
+      <c r="E72">
+        <v>474.9255032114394</v>
+      </c>
+      <c r="F72">
+        <v>570.4404925066417</v>
+      </c>
+      <c r="G72">
+        <v>62.6</v>
+      </c>
+      <c r="H72">
+        <v>719.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>74.616</v>
+      </c>
+      <c r="K72">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L72">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M72">
+        <v>136.221189610586</v>
+      </c>
+      <c r="N72">
+        <v>-78.10518961058602</v>
+      </c>
+      <c r="O72">
+        <v>-11.71577844158791</v>
+      </c>
+      <c r="P72">
+        <v>-66.38941116899812</v>
+      </c>
+      <c r="Q72">
+        <v>-49.88941116899813</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2029034028608394</v>
+      </c>
+      <c r="T72">
+        <v>2.301142108036164</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.06399444921102462</v>
+      </c>
+      <c r="W72">
+        <v>0.2235181255284073</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.4266296614068308</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.219333708728137</v>
+      </c>
+      <c r="C73">
+        <v>-281.4078313723921</v>
+      </c>
+      <c r="D73">
+        <v>234.5818110272014</v>
+      </c>
+      <c r="E73">
+        <v>483.0746531043912</v>
+      </c>
+      <c r="F73">
+        <v>578.5896423995936</v>
+      </c>
+      <c r="G73">
+        <v>62.6</v>
+      </c>
+      <c r="H73">
+        <v>719.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>74.616</v>
+      </c>
+      <c r="K73">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L73">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M73">
+        <v>138.167206605023</v>
+      </c>
+      <c r="N73">
+        <v>-80.05120660502294</v>
+      </c>
+      <c r="O73">
+        <v>-12.00768099075344</v>
+      </c>
+      <c r="P73">
+        <v>-68.0435256142695</v>
+      </c>
+      <c r="Q73">
+        <v>-51.54352561426951</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2085621408905235</v>
+      </c>
+      <c r="T73">
+        <v>2.38049183589948</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.06309311894044682</v>
+      </c>
+      <c r="W73">
+        <v>0.2237333631970213</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.420620792936312</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.221333708728137</v>
+      </c>
+      <c r="C74">
+        <v>-292.057803710363</v>
+      </c>
+      <c r="D74">
+        <v>232.0809885821827</v>
+      </c>
+      <c r="E74">
+        <v>491.2238029973433</v>
+      </c>
+      <c r="F74">
+        <v>586.7387922925457</v>
+      </c>
+      <c r="G74">
+        <v>62.6</v>
+      </c>
+      <c r="H74">
+        <v>719.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>74.616</v>
+      </c>
+      <c r="K74">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L74">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M74">
+        <v>140.1132235994599</v>
+      </c>
+      <c r="N74">
+        <v>-81.99722359945989</v>
+      </c>
+      <c r="O74">
+        <v>-12.29958353991898</v>
+      </c>
+      <c r="P74">
+        <v>-69.6976400595409</v>
+      </c>
+      <c r="Q74">
+        <v>-53.19764005954091</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2146250744937565</v>
+      </c>
+      <c r="T74">
+        <v>2.465509401467318</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.06221682562182949</v>
+      </c>
+      <c r="W74">
+        <v>0.2239426220415071</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.4147788374788633</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.223333708728137</v>
+      </c>
+      <c r="C75">
+        <v>-302.6550171194326</v>
+      </c>
+      <c r="D75">
+        <v>229.632925066065</v>
+      </c>
+      <c r="E75">
+        <v>499.3729528902953</v>
+      </c>
+      <c r="F75">
+        <v>594.8879421854976</v>
+      </c>
+      <c r="G75">
+        <v>62.6</v>
+      </c>
+      <c r="H75">
+        <v>719.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>74.616</v>
+      </c>
+      <c r="K75">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L75">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M75">
+        <v>142.0592405938968</v>
+      </c>
+      <c r="N75">
+        <v>-83.94324059389683</v>
+      </c>
+      <c r="O75">
+        <v>-12.59148608908453</v>
+      </c>
+      <c r="P75">
+        <v>-71.35175450481231</v>
+      </c>
+      <c r="Q75">
+        <v>-54.85175450481231</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2211371142898216</v>
+      </c>
+      <c r="T75">
+        <v>2.556824564484627</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.06136454033933868</v>
+      </c>
+      <c r="W75">
+        <v>0.2241461477669659</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.4090969355955912</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2253337087281369</v>
+      </c>
+      <c r="C76">
+        <v>-313.2011237259521</v>
+      </c>
+      <c r="D76">
+        <v>227.2359683524976</v>
+      </c>
+      <c r="E76">
+        <v>507.5221027832474</v>
+      </c>
+      <c r="F76">
+        <v>603.0370920784497</v>
+      </c>
+      <c r="G76">
+        <v>62.6</v>
+      </c>
+      <c r="H76">
+        <v>719.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>74.616</v>
+      </c>
+      <c r="K76">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L76">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M76">
+        <v>144.0052575883338</v>
+      </c>
+      <c r="N76">
+        <v>-85.88925758833381</v>
+      </c>
+      <c r="O76">
+        <v>-12.88338863825007</v>
+      </c>
+      <c r="P76">
+        <v>-73.00586895008374</v>
+      </c>
+      <c r="Q76">
+        <v>-56.50586895008374</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2281500802240454</v>
+      </c>
+      <c r="T76">
+        <v>2.655163970810958</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.06053528979421247</v>
+      </c>
+      <c r="W76">
+        <v>0.2243441727971421</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.4035685986280831</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.227333708728137</v>
+      </c>
+      <c r="C77">
+        <v>-323.6977073879037</v>
+      </c>
+      <c r="D77">
+        <v>224.888534583498</v>
+      </c>
+      <c r="E77">
+        <v>515.6712526761994</v>
+      </c>
+      <c r="F77">
+        <v>611.1862419714017</v>
+      </c>
+      <c r="G77">
+        <v>62.6</v>
+      </c>
+      <c r="H77">
+        <v>719.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>74.616</v>
+      </c>
+      <c r="K77">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L77">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M77">
+        <v>145.9512745827707</v>
+      </c>
+      <c r="N77">
+        <v>-87.83527458277072</v>
+      </c>
+      <c r="O77">
+        <v>-13.17529118741561</v>
+      </c>
+      <c r="P77">
+        <v>-74.65998339535511</v>
+      </c>
+      <c r="Q77">
+        <v>-58.15998339535512</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2357240834330073</v>
+      </c>
+      <c r="T77">
+        <v>2.761370529643397</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.05972815259695632</v>
+      </c>
+      <c r="W77">
+        <v>0.2245369171598469</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3981876839797087</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.229333708728137</v>
+      </c>
+      <c r="C78">
+        <v>-334.1462871850383</v>
+      </c>
+      <c r="D78">
+        <v>222.5891046793154</v>
+      </c>
+      <c r="E78">
+        <v>523.8204025691514</v>
+      </c>
+      <c r="F78">
+        <v>619.3353918643537</v>
+      </c>
+      <c r="G78">
+        <v>62.6</v>
+      </c>
+      <c r="H78">
+        <v>719.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>74.616</v>
+      </c>
+      <c r="K78">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L78">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M78">
+        <v>147.8972915772077</v>
+      </c>
+      <c r="N78">
+        <v>-89.78129157720767</v>
+      </c>
+      <c r="O78">
+        <v>-13.46719373658115</v>
+      </c>
+      <c r="P78">
+        <v>-76.31409784062652</v>
+      </c>
+      <c r="Q78">
+        <v>-59.81409784062652</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2439292535760492</v>
+      </c>
+      <c r="T78">
+        <v>2.876427635045205</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.05894225585225952</v>
+      </c>
+      <c r="W78">
+        <v>0.2247245893024804</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3929483723483967</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.231333708728137</v>
+      </c>
+      <c r="C79">
+        <v>-344.5483206970636</v>
+      </c>
+      <c r="D79">
+        <v>220.3362210602423</v>
+      </c>
+      <c r="E79">
+        <v>531.9695524621035</v>
+      </c>
+      <c r="F79">
+        <v>627.4845417573058</v>
+      </c>
+      <c r="G79">
+        <v>62.6</v>
+      </c>
+      <c r="H79">
+        <v>719.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>74.616</v>
+      </c>
+      <c r="K79">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L79">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M79">
+        <v>149.8433085716446</v>
+      </c>
+      <c r="N79">
+        <v>-91.72730857164461</v>
+      </c>
+      <c r="O79">
+        <v>-13.75909628574669</v>
+      </c>
+      <c r="P79">
+        <v>-77.96821228589792</v>
+      </c>
+      <c r="Q79">
+        <v>-61.46821228589793</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.252847916775008</v>
+      </c>
+      <c r="T79">
+        <v>3.001489706134127</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.05817677201002239</v>
+      </c>
+      <c r="W79">
+        <v>0.2249073868440067</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3878451467334826</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2333337087281369</v>
+      </c>
+      <c r="C80">
+        <v>-354.9052070847503</v>
+      </c>
+      <c r="D80">
+        <v>218.1284845655075</v>
+      </c>
+      <c r="E80">
+        <v>540.1187023550555</v>
+      </c>
+      <c r="F80">
+        <v>635.6336916502578</v>
+      </c>
+      <c r="G80">
+        <v>62.6</v>
+      </c>
+      <c r="H80">
+        <v>719.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>74.616</v>
+      </c>
+      <c r="K80">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L80">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M80">
+        <v>151.7893255660816</v>
+      </c>
+      <c r="N80">
+        <v>-93.67332556608156</v>
+      </c>
+      <c r="O80">
+        <v>-14.05099883491224</v>
+      </c>
+      <c r="P80">
+        <v>-79.62232673116932</v>
+      </c>
+      <c r="Q80">
+        <v>-63.12232673116933</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2625773675375083</v>
+      </c>
+      <c r="T80">
+        <v>3.137921056412951</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.05743091595861183</v>
+      </c>
+      <c r="W80">
+        <v>0.2250854972690835</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3828727730574123</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2353337087281369</v>
+      </c>
+      <c r="C81">
+        <v>-365.2182899876448</v>
+      </c>
+      <c r="D81">
+        <v>215.964551555565</v>
+      </c>
+      <c r="E81">
+        <v>548.2678522480076</v>
+      </c>
+      <c r="F81">
+        <v>643.7828415432099</v>
+      </c>
+      <c r="G81">
+        <v>62.6</v>
+      </c>
+      <c r="H81">
+        <v>719.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>74.616</v>
+      </c>
+      <c r="K81">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L81">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M81">
+        <v>153.7353425605185</v>
+      </c>
+      <c r="N81">
+        <v>-95.6193425605185</v>
+      </c>
+      <c r="O81">
+        <v>-14.34290138407778</v>
+      </c>
+      <c r="P81">
+        <v>-81.27644117644073</v>
+      </c>
+      <c r="Q81">
+        <v>-64.77644117644073</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.273233432658342</v>
+      </c>
+      <c r="T81">
+        <v>3.287345868623092</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.05670394233888258</v>
+      </c>
+      <c r="W81">
+        <v>0.2252590985694748</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3780262822592172</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2373337087281369</v>
+      </c>
+      <c r="C82">
+        <v>-375.4888602509937</v>
+      </c>
+      <c r="D82">
+        <v>213.8431311851682</v>
+      </c>
+      <c r="E82">
+        <v>556.4170021409595</v>
+      </c>
+      <c r="F82">
+        <v>651.9319914361619</v>
+      </c>
+      <c r="G82">
+        <v>62.6</v>
+      </c>
+      <c r="H82">
+        <v>719.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>74.616</v>
+      </c>
+      <c r="K82">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L82">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M82">
+        <v>155.6813595549555</v>
+      </c>
+      <c r="N82">
+        <v>-97.56535955495545</v>
+      </c>
+      <c r="O82">
+        <v>-14.63480393324332</v>
+      </c>
+      <c r="P82">
+        <v>-82.93055562171213</v>
+      </c>
+      <c r="Q82">
+        <v>-66.43055562171213</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2849551042912591</v>
+      </c>
+      <c r="T82">
+        <v>3.451713162054247</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.05599514305964654</v>
+      </c>
+      <c r="W82">
+        <v>0.2254283598373564</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3733009537309769</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.239333708728137</v>
+      </c>
+      <c r="C83">
+        <v>-385.7181584935135</v>
+      </c>
+      <c r="D83">
+        <v>211.7629828356005</v>
+      </c>
+      <c r="E83">
+        <v>564.5661520339116</v>
+      </c>
+      <c r="F83">
+        <v>660.081141329114</v>
+      </c>
+      <c r="G83">
+        <v>62.6</v>
+      </c>
+      <c r="H83">
+        <v>719.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>74.616</v>
+      </c>
+      <c r="K83">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L83">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M83">
+        <v>157.6273765493924</v>
+      </c>
+      <c r="N83">
+        <v>-99.51137654939239</v>
+      </c>
+      <c r="O83">
+        <v>-14.92670648240886</v>
+      </c>
+      <c r="P83">
+        <v>-84.58467006698353</v>
+      </c>
+      <c r="Q83">
+        <v>-68.08467006698353</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2979106360960623</v>
+      </c>
+      <c r="T83">
+        <v>3.633382275846576</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.05530384499718177</v>
+      </c>
+      <c r="W83">
+        <v>0.225593441814673</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3686922999812118</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2413337087281369</v>
+      </c>
+      <c r="C84">
+        <v>-395.9073775267368</v>
+      </c>
+      <c r="D84">
+        <v>209.7229136953291</v>
+      </c>
+      <c r="E84">
+        <v>572.7153019268636</v>
+      </c>
+      <c r="F84">
+        <v>668.2302912220659</v>
+      </c>
+      <c r="G84">
+        <v>62.6</v>
+      </c>
+      <c r="H84">
+        <v>719.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>74.616</v>
+      </c>
+      <c r="K84">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L84">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M84">
+        <v>159.5733935438294</v>
+      </c>
+      <c r="N84">
+        <v>-101.4573935438293</v>
+      </c>
+      <c r="O84">
+        <v>-15.2186090315744</v>
+      </c>
+      <c r="P84">
+        <v>-86.23878451225494</v>
+      </c>
+      <c r="Q84">
+        <v>-69.73878451225494</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3123056714347324</v>
+      </c>
+      <c r="T84">
+        <v>3.835236846726941</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.0546294078630698</v>
+      </c>
+      <c r="W84">
+        <v>0.2257544974022989</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3641960524204653</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.243333708728137</v>
+      </c>
+      <c r="C85">
+        <v>-406.0576646358494</v>
+      </c>
+      <c r="D85">
+        <v>207.7217764791685</v>
+      </c>
+      <c r="E85">
+        <v>580.8644518198156</v>
+      </c>
+      <c r="F85">
+        <v>676.3794411150179</v>
+      </c>
+      <c r="G85">
+        <v>62.6</v>
+      </c>
+      <c r="H85">
+        <v>719.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>74.616</v>
+      </c>
+      <c r="K85">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L85">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M85">
+        <v>161.5194105382663</v>
+      </c>
+      <c r="N85">
+        <v>-103.4034105382663</v>
+      </c>
+      <c r="O85">
+        <v>-15.51051158073994</v>
+      </c>
+      <c r="P85">
+        <v>-87.89289895752634</v>
+      </c>
+      <c r="Q85">
+        <v>-71.39289895752634</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3283942403426579</v>
+      </c>
+      <c r="T85">
+        <v>4.060839014181468</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.05397122222616534</v>
+      </c>
+      <c r="W85">
+        <v>0.2259116721323917</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3598081481744356</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2453337087281369</v>
+      </c>
+      <c r="C86">
+        <v>-416.1701237311802</v>
+      </c>
+      <c r="D86">
+        <v>205.7584672767896</v>
+      </c>
+      <c r="E86">
+        <v>589.0136017127676</v>
+      </c>
+      <c r="F86">
+        <v>684.5285910079699</v>
+      </c>
+      <c r="G86">
+        <v>62.6</v>
+      </c>
+      <c r="H86">
+        <v>719.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>74.616</v>
+      </c>
+      <c r="K86">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L86">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M86">
+        <v>163.4654275327032</v>
+      </c>
+      <c r="N86">
+        <v>-105.3494275327032</v>
+      </c>
+      <c r="O86">
+        <v>-15.80241412990548</v>
+      </c>
+      <c r="P86">
+        <v>-89.54701340279772</v>
+      </c>
+      <c r="Q86">
+        <v>-73.04701340279772</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3464938803640738</v>
+      </c>
+      <c r="T86">
+        <v>4.314641452567807</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.05332870767585386</v>
+      </c>
+      <c r="W86">
+        <v>0.2260651046070061</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3555247178390257</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2473337087281369</v>
+      </c>
+      <c r="C87">
+        <v>-426.2458173788244</v>
+      </c>
+      <c r="D87">
+        <v>203.8319235220974</v>
+      </c>
+      <c r="E87">
+        <v>597.1627516057196</v>
+      </c>
+      <c r="F87">
+        <v>692.6777409009219</v>
+      </c>
+      <c r="G87">
+        <v>62.6</v>
+      </c>
+      <c r="H87">
+        <v>719.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>74.616</v>
+      </c>
+      <c r="K87">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L87">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M87">
+        <v>165.4114445271402</v>
+      </c>
+      <c r="N87">
+        <v>-107.2954445271401</v>
+      </c>
+      <c r="O87">
+        <v>-16.09431667907102</v>
+      </c>
+      <c r="P87">
+        <v>-91.20112784806912</v>
+      </c>
+      <c r="Q87">
+        <v>-74.70112784806912</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3670068057216788</v>
+      </c>
+      <c r="T87">
+        <v>4.602284216072328</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.05270131111496146</v>
+      </c>
+      <c r="W87">
+        <v>0.2262149269057472</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3513420740997431</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2493337087281369</v>
+      </c>
+      <c r="C88">
+        <v>-436.2857687182462</v>
+      </c>
+      <c r="D88">
+        <v>201.9411220756278</v>
+      </c>
+      <c r="E88">
+        <v>605.3119014986717</v>
+      </c>
+      <c r="F88">
+        <v>700.826890793874</v>
+      </c>
+      <c r="G88">
+        <v>62.6</v>
+      </c>
+      <c r="H88">
+        <v>719.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>74.616</v>
+      </c>
+      <c r="K88">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L88">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M88">
+        <v>167.3574615215771</v>
+      </c>
+      <c r="N88">
+        <v>-109.2414615215771</v>
+      </c>
+      <c r="O88">
+        <v>-16.38621922823657</v>
+      </c>
+      <c r="P88">
+        <v>-92.85524229334052</v>
+      </c>
+      <c r="Q88">
+        <v>-76.35524229334052</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.390450148987513</v>
+      </c>
+      <c r="T88">
+        <v>4.931018802934637</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.05208850517176424</v>
+      </c>
+      <c r="W88">
+        <v>0.2263612649649827</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3472567011450949</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.251333708728137</v>
+      </c>
+      <c r="C89">
+        <v>-446.290963274133</v>
+      </c>
+      <c r="D89">
+        <v>200.0850774126929</v>
+      </c>
+      <c r="E89">
+        <v>613.4610513916236</v>
+      </c>
+      <c r="F89">
+        <v>708.976040686826</v>
+      </c>
+      <c r="G89">
+        <v>62.6</v>
+      </c>
+      <c r="H89">
+        <v>719.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>74.616</v>
+      </c>
+      <c r="K89">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L89">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M89">
+        <v>169.3034785160141</v>
+      </c>
+      <c r="N89">
+        <v>-111.187478516014</v>
+      </c>
+      <c r="O89">
+        <v>-16.67812177740211</v>
+      </c>
+      <c r="P89">
+        <v>-94.50935673861193</v>
+      </c>
+      <c r="Q89">
+        <v>-78.00935673861193</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4175001604480909</v>
+      </c>
+      <c r="T89">
+        <v>5.310327941621916</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.05148978672151407</v>
+      </c>
+      <c r="W89">
+        <v>0.2265042389309025</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3432652448100938</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.253333708728137</v>
+      </c>
+      <c r="C90">
+        <v>-456.262350669244</v>
+      </c>
+      <c r="D90">
+        <v>198.262839910534</v>
+      </c>
+      <c r="E90">
+        <v>621.6102012845757</v>
+      </c>
+      <c r="F90">
+        <v>717.1251905797781</v>
+      </c>
+      <c r="G90">
+        <v>62.6</v>
+      </c>
+      <c r="H90">
+        <v>719.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>74.616</v>
+      </c>
+      <c r="K90">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L90">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M90">
+        <v>171.249495510451</v>
+      </c>
+      <c r="N90">
+        <v>-113.133495510451</v>
+      </c>
+      <c r="O90">
+        <v>-16.97002432656765</v>
+      </c>
+      <c r="P90">
+        <v>-96.16347118388333</v>
+      </c>
+      <c r="Q90">
+        <v>-79.66347118388333</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4490585071520986</v>
+      </c>
+      <c r="T90">
+        <v>5.752855270090412</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.05090467550876959</v>
+      </c>
+      <c r="W90">
+        <v>0.2266439634885059</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3393645033917972</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2553337087281369</v>
+      </c>
+      <c r="C91">
+        <v>-466.2008462445049</v>
+      </c>
+      <c r="D91">
+        <v>196.4734942282251</v>
+      </c>
+      <c r="E91">
+        <v>629.7593511775277</v>
+      </c>
+      <c r="F91">
+        <v>725.27434047273</v>
+      </c>
+      <c r="G91">
+        <v>62.6</v>
+      </c>
+      <c r="H91">
+        <v>719.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>74.616</v>
+      </c>
+      <c r="K91">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L91">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M91">
+        <v>173.1955125048879</v>
+      </c>
+      <c r="N91">
+        <v>-115.0795125048879</v>
+      </c>
+      <c r="O91">
+        <v>-17.26192687573319</v>
+      </c>
+      <c r="P91">
+        <v>-97.81758562915473</v>
+      </c>
+      <c r="Q91">
+        <v>-81.31758562915473</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4863547350750165</v>
+      </c>
+      <c r="T91">
+        <v>6.275842112825902</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.05033271286260364</v>
+      </c>
+      <c r="W91">
+        <v>0.2267805481684103</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3355514190840242</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.257333708728137</v>
+      </c>
+      <c r="C92">
+        <v>-476.1073325921607</v>
+      </c>
+      <c r="D92">
+        <v>194.7161577735215</v>
+      </c>
+      <c r="E92">
+        <v>637.9085010704798</v>
+      </c>
+      <c r="F92">
+        <v>733.4234903656821</v>
+      </c>
+      <c r="G92">
+        <v>62.6</v>
+      </c>
+      <c r="H92">
+        <v>719.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>74.616</v>
+      </c>
+      <c r="K92">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L92">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M92">
+        <v>175.1415294993249</v>
+      </c>
+      <c r="N92">
+        <v>-117.0255294993249</v>
+      </c>
+      <c r="O92">
+        <v>-17.55382942489874</v>
+      </c>
+      <c r="P92">
+        <v>-99.47170007442617</v>
+      </c>
+      <c r="Q92">
+        <v>-82.97170007442617</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5311102085825183</v>
+      </c>
+      <c r="T92">
+        <v>6.903426324108493</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.04977346049746358</v>
+      </c>
+      <c r="W92">
+        <v>0.2269140976332057</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3318230699830905</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2593337087281369</v>
+      </c>
+      <c r="C93">
+        <v>-485.9826610073756</v>
+      </c>
+      <c r="D93">
+        <v>192.9899792512585</v>
+      </c>
+      <c r="E93">
+        <v>646.0576509634318</v>
+      </c>
+      <c r="F93">
+        <v>741.5726402586341</v>
+      </c>
+      <c r="G93">
+        <v>62.6</v>
+      </c>
+      <c r="H93">
+        <v>719.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>74.616</v>
+      </c>
+      <c r="K93">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L93">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M93">
+        <v>177.0875464937618</v>
+      </c>
+      <c r="N93">
+        <v>-118.9715464937618</v>
+      </c>
+      <c r="O93">
+        <v>-17.84573197406428</v>
+      </c>
+      <c r="P93">
+        <v>-101.1258145196975</v>
+      </c>
+      <c r="Q93">
+        <v>-84.62581451969754</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5858113428694647</v>
+      </c>
+      <c r="T93">
+        <v>7.670473693453882</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.04922649939309586</v>
+      </c>
+      <c r="W93">
+        <v>0.2270447119449287</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.328176662620639</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2613337087281369</v>
+      </c>
+      <c r="C94">
+        <v>-495.8276528633039</v>
+      </c>
+      <c r="D94">
+        <v>191.2941372882822</v>
+      </c>
+      <c r="E94">
+        <v>654.2068008563838</v>
+      </c>
+      <c r="F94">
+        <v>749.7217901515861</v>
+      </c>
+      <c r="G94">
+        <v>62.6</v>
+      </c>
+      <c r="H94">
+        <v>719.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>74.616</v>
+      </c>
+      <c r="K94">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L94">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M94">
+        <v>179.0335634881988</v>
+      </c>
+      <c r="N94">
+        <v>-120.9175634881988</v>
+      </c>
+      <c r="O94">
+        <v>-18.13763452322982</v>
+      </c>
+      <c r="P94">
+        <v>-102.7799289649689</v>
+      </c>
+      <c r="Q94">
+        <v>-86.27992896496895</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.6541877607281481</v>
+      </c>
+      <c r="T94">
+        <v>8.62928290513562</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.04869142874751874</v>
+      </c>
+      <c r="W94">
+        <v>0.2271724868150925</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3246095249834582</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2633337087281369</v>
+      </c>
+      <c r="C95">
+        <v>-505.6431009142912</v>
+      </c>
+      <c r="D95">
+        <v>189.6278391302471</v>
+      </c>
+      <c r="E95">
+        <v>662.3559507493359</v>
+      </c>
+      <c r="F95">
+        <v>757.8709400445382</v>
+      </c>
+      <c r="G95">
+        <v>62.6</v>
+      </c>
+      <c r="H95">
+        <v>719.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>74.616</v>
+      </c>
+      <c r="K95">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L95">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M95">
+        <v>180.9795804826357</v>
+      </c>
+      <c r="N95">
+        <v>-122.8635804826357</v>
+      </c>
+      <c r="O95">
+        <v>-18.42953707239536</v>
+      </c>
+      <c r="P95">
+        <v>-104.4340434102403</v>
+      </c>
+      <c r="Q95">
+        <v>-87.93404341024035</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.7421002979750264</v>
+      </c>
+      <c r="T95">
+        <v>9.862037605869281</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.04816786499754541</v>
+      </c>
+      <c r="W95">
+        <v>0.2272975138385862</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3211190999836361</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.265333708728137</v>
+      </c>
+      <c r="C96">
+        <v>-515.4297705315537</v>
+      </c>
+      <c r="D96">
+        <v>187.9903194059364</v>
+      </c>
+      <c r="E96">
+        <v>670.5051006422879</v>
+      </c>
+      <c r="F96">
+        <v>766.0200899374902</v>
+      </c>
+      <c r="G96">
+        <v>62.6</v>
+      </c>
+      <c r="H96">
+        <v>719.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>74.616</v>
+      </c>
+      <c r="K96">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L96">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M96">
+        <v>182.9255974770727</v>
+      </c>
+      <c r="N96">
+        <v>-124.8095974770727</v>
+      </c>
+      <c r="O96">
+        <v>-18.7214396215609</v>
+      </c>
+      <c r="P96">
+        <v>-106.0881578555118</v>
+      </c>
+      <c r="Q96">
+        <v>-89.58815785551175</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.8593170143041977</v>
+      </c>
+      <c r="T96">
+        <v>11.50571054018083</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.04765544090182684</v>
+      </c>
+      <c r="W96">
+        <v>0.2274198807126438</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3177029393455123</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2673337087281369</v>
+      </c>
+      <c r="C97">
+        <v>-525.1884008753843</v>
+      </c>
+      <c r="D97">
+        <v>186.380838955058</v>
+      </c>
+      <c r="E97">
+        <v>678.65425053524</v>
+      </c>
+      <c r="F97">
+        <v>774.1692398304423</v>
+      </c>
+      <c r="G97">
+        <v>62.6</v>
+      </c>
+      <c r="H97">
+        <v>719.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>74.616</v>
+      </c>
+      <c r="K97">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L97">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M97">
+        <v>184.8716144715096</v>
+      </c>
+      <c r="N97">
+        <v>-126.7556144715096</v>
+      </c>
+      <c r="O97">
+        <v>-19.01334217072644</v>
+      </c>
+      <c r="P97">
+        <v>-107.7422723007832</v>
+      </c>
+      <c r="Q97">
+        <v>-91.24227230078316</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.023420417165038</v>
+      </c>
+      <c r="T97">
+        <v>13.806852648217</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.04715380468180762</v>
+      </c>
+      <c r="W97">
+        <v>0.2275396714419843</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3143586978787174</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2693337087281369</v>
+      </c>
+      <c r="C98">
+        <v>-534.9197060076509</v>
+      </c>
+      <c r="D98">
+        <v>184.7986837157432</v>
+      </c>
+      <c r="E98">
+        <v>686.8034004281918</v>
+      </c>
+      <c r="F98">
+        <v>782.3183897233941</v>
+      </c>
+      <c r="G98">
+        <v>62.6</v>
+      </c>
+      <c r="H98">
+        <v>719.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>74.616</v>
+      </c>
+      <c r="K98">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L98">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M98">
+        <v>186.8176314659465</v>
+      </c>
+      <c r="N98">
+        <v>-128.7016314659465</v>
+      </c>
+      <c r="O98">
+        <v>-19.30524471989198</v>
+      </c>
+      <c r="P98">
+        <v>-109.3963867460545</v>
+      </c>
+      <c r="Q98">
+        <v>-92.89638674605453</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.269575521456294</v>
+      </c>
+      <c r="T98">
+        <v>17.25856581027122</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.04666261921637212</v>
+      </c>
+      <c r="W98">
+        <v>0.2276569665311304</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3110841281091475</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2713337087281369</v>
+      </c>
+      <c r="C99">
+        <v>-544.6243759481131</v>
+      </c>
+      <c r="D99">
+        <v>183.2431636682332</v>
+      </c>
+      <c r="E99">
+        <v>694.9525503211439</v>
+      </c>
+      <c r="F99">
+        <v>790.4675396163462</v>
+      </c>
+      <c r="G99">
+        <v>62.6</v>
+      </c>
+      <c r="H99">
+        <v>719.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>74.616</v>
+      </c>
+      <c r="K99">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L99">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M99">
+        <v>188.7636484603835</v>
+      </c>
+      <c r="N99">
+        <v>-130.6476484603835</v>
+      </c>
+      <c r="O99">
+        <v>-19.59714726905752</v>
+      </c>
+      <c r="P99">
+        <v>-111.0505011913259</v>
+      </c>
+      <c r="Q99">
+        <v>-94.55050119132594</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.679834028608393</v>
+      </c>
+      <c r="T99">
+        <v>23.01142108036162</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.04618156128630643</v>
+      </c>
+      <c r="W99">
+        <v>0.22777184316483</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3078770752420429</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2733337087281369</v>
+      </c>
+      <c r="C100">
+        <v>-554.3030776778307</v>
+      </c>
+      <c r="D100">
+        <v>181.7136118314675</v>
+      </c>
+      <c r="E100">
+        <v>703.1017002140959</v>
+      </c>
+      <c r="F100">
+        <v>798.6166895092982</v>
+      </c>
+      <c r="G100">
+        <v>62.6</v>
+      </c>
+      <c r="H100">
+        <v>719.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>74.616</v>
+      </c>
+      <c r="K100">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L100">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M100">
+        <v>190.7096654548204</v>
+      </c>
+      <c r="N100">
+        <v>-132.5936654548204</v>
+      </c>
+      <c r="O100">
+        <v>-19.88904981822306</v>
+      </c>
+      <c r="P100">
+        <v>-112.7046156365973</v>
+      </c>
+      <c r="Q100">
+        <v>-96.20461563659734</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.500351042912589</v>
+      </c>
+      <c r="T100">
+        <v>34.51713162054244</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.04571032086501759</v>
+      </c>
+      <c r="W100">
+        <v>0.2278843753774338</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3047354724334506</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2753337087281369</v>
+      </c>
+      <c r="C101">
+        <v>-563.9564560927402</v>
+      </c>
+      <c r="D101">
+        <v>180.2093833095102</v>
+      </c>
+      <c r="E101">
+        <v>711.250850107048</v>
+      </c>
+      <c r="F101">
+        <v>806.7658394022503</v>
+      </c>
+      <c r="G101">
+        <v>62.6</v>
+      </c>
+      <c r="H101">
+        <v>719.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>74.616</v>
+      </c>
+      <c r="K101">
+        <v>16.49999999999999</v>
+      </c>
+      <c r="L101">
+        <v>58.11600000000001</v>
+      </c>
+      <c r="M101">
+        <v>192.6556824492574</v>
+      </c>
+      <c r="N101">
+        <v>-134.5396824492574</v>
+      </c>
+      <c r="O101">
+        <v>-20.18095236738861</v>
+      </c>
+      <c r="P101">
+        <v>-114.3587300818688</v>
+      </c>
+      <c r="Q101">
+        <v>-97.85873008186877</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.961902085825178</v>
+      </c>
+      <c r="T101">
+        <v>69.03426324108487</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.04524860045223963</v>
+      </c>
+      <c r="W101">
+        <v>0.2279946342120052</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3016573363482642</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
